--- a/pca-interpretable-clustering/classified_data/Oxide.xlsx
+++ b/pca-interpretable-clustering/classified_data/Oxide.xlsx
@@ -7125,7 +7125,7 @@
         <v>99.65611</v>
       </c>
       <c r="H2">
-        <v>547.93573</v>
+        <v>547.935733</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -7151,7 +7151,7 @@
         <v>34.59772</v>
       </c>
       <c r="H3">
-        <v>239.16261</v>
+        <v>239.1626063</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -7177,7 +7177,7 @@
         <v>291.63792</v>
       </c>
       <c r="H4">
-        <v>903.58098</v>
+        <v>903.5809757</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -7203,7 +7203,7 @@
         <v>17.50742</v>
       </c>
       <c r="H5">
-        <v>332.66909</v>
+        <v>332.6690936</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -7229,7 +7229,7 @@
         <v>121.91488</v>
       </c>
       <c r="H6">
-        <v>569.8791</v>
+        <v>632.7593987</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -7255,7 +7255,7 @@
         <v>31.30538</v>
       </c>
       <c r="H7">
-        <v>303.61936</v>
+        <v>303.6193565</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -7281,7 +7281,7 @@
         <v>80.98884</v>
       </c>
       <c r="H8">
-        <v>488.56365</v>
+        <v>488.5636504</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -7307,7 +7307,7 @@
         <v>130.3106</v>
       </c>
       <c r="H9">
-        <v>744.1165099999999</v>
+        <v>744.1165134</v>
       </c>
     </row>
     <row r="10" spans="1:8">
@@ -7333,7 +7333,7 @@
         <v>51.08269</v>
       </c>
       <c r="H10">
-        <v>274.82659</v>
+        <v>274.8265925</v>
       </c>
     </row>
     <row r="11" spans="1:8">
@@ -7359,7 +7359,7 @@
         <v>76.71974</v>
       </c>
       <c r="H11">
-        <v>500.56548</v>
+        <v>500.5654767</v>
       </c>
     </row>
     <row r="12" spans="1:8">
@@ -7385,7 +7385,7 @@
         <v>109.32372</v>
       </c>
       <c r="H12">
-        <v>524.33023</v>
+        <v>524.3302308</v>
       </c>
     </row>
     <row r="13" spans="1:8">
@@ -7411,7 +7411,7 @@
         <v>48.3704</v>
       </c>
       <c r="H13">
-        <v>268.64286</v>
+        <v>268.6428564</v>
       </c>
     </row>
     <row r="14" spans="1:8">
@@ -7437,7 +7437,7 @@
         <v>116.39929</v>
       </c>
       <c r="H14">
-        <v>499.81073</v>
+        <v>499.8107334</v>
       </c>
     </row>
     <row r="15" spans="1:8">
@@ -7463,7 +7463,7 @@
         <v>93.14281</v>
       </c>
       <c r="H15">
-        <v>363.56009</v>
+        <v>363.5600864</v>
       </c>
     </row>
     <row r="16" spans="1:8">
@@ -7489,7 +7489,7 @@
         <v>69.24588</v>
       </c>
       <c r="H16">
-        <v>500.78921</v>
+        <v>500.7892051</v>
       </c>
     </row>
     <row r="17" spans="1:8">
@@ -7515,7 +7515,7 @@
         <v>117.69598</v>
       </c>
       <c r="H17">
-        <v>501.36711</v>
+        <v>501.3671057</v>
       </c>
     </row>
     <row r="18" spans="1:8">
@@ -7541,7 +7541,7 @@
         <v>24.954</v>
       </c>
       <c r="H18">
-        <v>172.12529</v>
+        <v>172.1252896</v>
       </c>
     </row>
     <row r="19" spans="1:8">
@@ -7567,7 +7567,7 @@
         <v>21.39311</v>
       </c>
       <c r="H19">
-        <v>140.9797</v>
+        <v>140.9797034</v>
       </c>
     </row>
     <row r="20" spans="1:8">
@@ -7593,7 +7593,7 @@
         <v>90.0706</v>
       </c>
       <c r="H20">
-        <v>461.06513</v>
+        <v>461.0651348</v>
       </c>
     </row>
     <row r="21" spans="1:8">
@@ -7619,7 +7619,7 @@
         <v>57.93843</v>
       </c>
       <c r="H21">
-        <v>330.32475</v>
+        <v>330.3247528</v>
       </c>
     </row>
     <row r="22" spans="1:8">
@@ -7645,7 +7645,7 @@
         <v>18.85331</v>
       </c>
       <c r="H22">
-        <v>164.13152</v>
+        <v>164.1315201</v>
       </c>
     </row>
     <row r="23" spans="1:8">
@@ -7671,7 +7671,7 @@
         <v>50.60141</v>
       </c>
       <c r="H23">
-        <v>366.9964</v>
+        <v>366.9964044</v>
       </c>
     </row>
     <row r="24" spans="1:8">
@@ -7697,7 +7697,7 @@
         <v>144.14476</v>
       </c>
       <c r="H24">
-        <v>516.00275</v>
+        <v>516.0027493</v>
       </c>
     </row>
     <row r="25" spans="1:8">
@@ -7723,7 +7723,7 @@
         <v>23.35621</v>
       </c>
       <c r="H25">
-        <v>202.04463</v>
+        <v>202.0446319</v>
       </c>
     </row>
     <row r="26" spans="1:8">
@@ -7749,7 +7749,7 @@
         <v>52.2691</v>
       </c>
       <c r="H26">
-        <v>240.36572</v>
+        <v>240.3657217</v>
       </c>
     </row>
     <row r="27" spans="1:8">
@@ -7775,7 +7775,7 @@
         <v>113.15184</v>
       </c>
       <c r="H27">
-        <v>516.2231</v>
+        <v>516.2230979</v>
       </c>
     </row>
     <row r="28" spans="1:8">
@@ -7801,7 +7801,7 @@
         <v>28.88547</v>
       </c>
       <c r="H28">
-        <v>205.09106</v>
+        <v>205.0910622</v>
       </c>
     </row>
     <row r="29" spans="1:8">
@@ -7827,7 +7827,7 @@
         <v>129.42556</v>
       </c>
       <c r="H29">
-        <v>369.70208</v>
+        <v>369.7020785</v>
       </c>
     </row>
     <row r="30" spans="1:8">
@@ -7853,7 +7853,7 @@
         <v>168.73795</v>
       </c>
       <c r="H30">
-        <v>470.97372</v>
+        <v>470.9737154</v>
       </c>
     </row>
     <row r="31" spans="1:8">
@@ -7879,7 +7879,7 @@
         <v>14.6987</v>
       </c>
       <c r="H31">
-        <v>125.58407</v>
+        <v>125.5840748</v>
       </c>
     </row>
     <row r="32" spans="1:8">
@@ -7905,7 +7905,7 @@
         <v>143.83685</v>
       </c>
       <c r="H32">
-        <v>531.39244</v>
+        <v>586.9285795</v>
       </c>
     </row>
     <row r="33" spans="1:8">
@@ -7931,7 +7931,7 @@
         <v>75.78681</v>
       </c>
       <c r="H33">
-        <v>402.78372</v>
+        <v>387.6769714</v>
       </c>
     </row>
     <row r="34" spans="1:8">
@@ -7957,7 +7957,7 @@
         <v>157.97786</v>
       </c>
       <c r="H34">
-        <v>651.89616</v>
+        <v>651.8961561</v>
       </c>
     </row>
     <row r="35" spans="1:8">
@@ -7983,7 +7983,7 @@
         <v>168.6835</v>
       </c>
       <c r="H35">
-        <v>601.6501</v>
+        <v>642.7893688</v>
       </c>
     </row>
     <row r="36" spans="1:8">
@@ -8009,7 +8009,7 @@
         <v>105.34193</v>
       </c>
       <c r="H36">
-        <v>476.97366</v>
+        <v>528.0342061</v>
       </c>
     </row>
     <row r="37" spans="1:8">
@@ -8035,7 +8035,7 @@
         <v>125.28335</v>
       </c>
       <c r="H37">
-        <v>512.52161</v>
+        <v>512.521611</v>
       </c>
     </row>
     <row r="38" spans="1:8">
@@ -8061,7 +8061,7 @@
         <v>93.95953</v>
       </c>
       <c r="H38">
-        <v>406.91046</v>
+        <v>404.8647609</v>
       </c>
     </row>
     <row r="39" spans="1:8">
@@ -8087,7 +8087,7 @@
         <v>92.22045</v>
       </c>
       <c r="H39">
-        <v>413.06271</v>
+        <v>413.0627076</v>
       </c>
     </row>
     <row r="40" spans="1:8">
@@ -8113,7 +8113,7 @@
         <v>92.05825</v>
       </c>
       <c r="H40">
-        <v>414.60334</v>
+        <v>414.603344</v>
       </c>
     </row>
     <row r="41" spans="1:8">
@@ -8139,7 +8139,7 @@
         <v>69.08767</v>
       </c>
       <c r="H41">
-        <v>322.82473</v>
+        <v>400.4760785</v>
       </c>
     </row>
     <row r="42" spans="1:8">
@@ -8165,7 +8165,7 @@
         <v>79.5625</v>
       </c>
       <c r="H42">
-        <v>400.49736</v>
+        <v>457.6077214</v>
       </c>
     </row>
     <row r="43" spans="1:8">
@@ -8191,7 +8191,7 @@
         <v>195.41453</v>
       </c>
       <c r="H43">
-        <v>611.32857</v>
+        <v>611.328572</v>
       </c>
     </row>
     <row r="44" spans="1:8">
@@ -8217,7 +8217,7 @@
         <v>159.19124</v>
       </c>
       <c r="H44">
-        <v>499.20214</v>
+        <v>499.2021416</v>
       </c>
     </row>
     <row r="45" spans="1:8">
@@ -8243,7 +8243,7 @@
         <v>188.83858</v>
       </c>
       <c r="H45">
-        <v>684.69192</v>
+        <v>684.6919165</v>
       </c>
     </row>
     <row r="46" spans="1:8">
@@ -8269,7 +8269,7 @@
         <v>131.40459</v>
       </c>
       <c r="H46">
-        <v>538.25258</v>
+        <v>623.1454363</v>
       </c>
     </row>
     <row r="47" spans="1:8">
@@ -8295,7 +8295,7 @@
         <v>81.70094</v>
       </c>
       <c r="H47">
-        <v>324.17995</v>
+        <v>324.1799451</v>
       </c>
     </row>
     <row r="48" spans="1:8">
@@ -8321,7 +8321,7 @@
         <v>183.86112</v>
       </c>
       <c r="H48">
-        <v>527.7257</v>
+        <v>527.7257039</v>
       </c>
     </row>
     <row r="49" spans="1:8">
@@ -8347,7 +8347,7 @@
         <v>174.5628</v>
       </c>
       <c r="H49">
-        <v>388.90127</v>
+        <v>388.9012746</v>
       </c>
     </row>
     <row r="50" spans="1:8">
@@ -8373,7 +8373,7 @@
         <v>170.52207</v>
       </c>
       <c r="H50">
-        <v>391.12686</v>
+        <v>391.1268571</v>
       </c>
     </row>
     <row r="51" spans="1:8">
@@ -8399,7 +8399,7 @@
         <v>153.12186</v>
       </c>
       <c r="H51">
-        <v>359.56388</v>
+        <v>359.5638782</v>
       </c>
     </row>
     <row r="52" spans="1:8">
@@ -8425,7 +8425,7 @@
         <v>158.45762</v>
       </c>
       <c r="H52">
-        <v>452.70951</v>
+        <v>452.7095145</v>
       </c>
     </row>
     <row r="53" spans="1:8">
@@ -8451,7 +8451,7 @@
         <v>170.76472</v>
       </c>
       <c r="H53">
-        <v>400.21322</v>
+        <v>400.2132247</v>
       </c>
     </row>
     <row r="54" spans="1:8">
@@ -8477,7 +8477,7 @@
         <v>14.18555</v>
       </c>
       <c r="H54">
-        <v>141.76791</v>
+        <v>141.7679079</v>
       </c>
     </row>
     <row r="55" spans="1:8">
@@ -8503,7 +8503,7 @@
         <v>162.17095</v>
       </c>
       <c r="H55">
-        <v>527.10327</v>
+        <v>527.1032692</v>
       </c>
     </row>
     <row r="56" spans="1:8">
@@ -8529,7 +8529,7 @@
         <v>193.31792</v>
       </c>
       <c r="H56">
-        <v>481.82193</v>
+        <v>481.8219256</v>
       </c>
     </row>
     <row r="57" spans="1:8">
@@ -8555,7 +8555,7 @@
         <v>175.7023</v>
       </c>
       <c r="H57">
-        <v>401.43214</v>
+        <v>401.4321438</v>
       </c>
     </row>
     <row r="58" spans="1:8">
@@ -8581,7 +8581,7 @@
         <v>172.4053</v>
       </c>
       <c r="H58">
-        <v>431.08125</v>
+        <v>497.117905</v>
       </c>
     </row>
     <row r="59" spans="1:8">
@@ -8607,7 +8607,7 @@
         <v>23.72348</v>
       </c>
       <c r="H59">
-        <v>160.5328</v>
+        <v>160.5327951</v>
       </c>
     </row>
     <row r="60" spans="1:8">
@@ -8633,7 +8633,7 @@
         <v>49.02148</v>
       </c>
       <c r="H60">
-        <v>189.26841</v>
+        <v>189.2684147</v>
       </c>
     </row>
     <row r="61" spans="1:8">
@@ -8659,7 +8659,7 @@
         <v>55.59149</v>
       </c>
       <c r="H61">
-        <v>230.16913</v>
+        <v>230.1691276</v>
       </c>
     </row>
     <row r="62" spans="1:8">
@@ -8685,7 +8685,7 @@
         <v>63.64666</v>
       </c>
       <c r="H62">
-        <v>349.13392</v>
+        <v>349.1339229</v>
       </c>
     </row>
     <row r="63" spans="1:8">
@@ -8711,7 +8711,7 @@
         <v>34.04321</v>
       </c>
       <c r="H63">
-        <v>311.76336</v>
+        <v>311.7633635</v>
       </c>
     </row>
     <row r="64" spans="1:8">
@@ -8737,7 +8737,7 @@
         <v>129.16534</v>
       </c>
       <c r="H64">
-        <v>632.90672</v>
+        <v>632.9067233</v>
       </c>
     </row>
     <row r="65" spans="1:8">
@@ -8763,7 +8763,7 @@
         <v>171.72933</v>
       </c>
       <c r="H65">
-        <v>648.49568</v>
+        <v>648.4956793</v>
       </c>
     </row>
     <row r="66" spans="1:8">
@@ -8789,7 +8789,7 @@
         <v>128.16194</v>
       </c>
       <c r="H66">
-        <v>327.92306</v>
+        <v>327.9230582</v>
       </c>
     </row>
     <row r="67" spans="1:8">
@@ -8815,7 +8815,7 @@
         <v>94.77983</v>
       </c>
       <c r="H67">
-        <v>354.58056</v>
+        <v>354.5805638</v>
       </c>
     </row>
     <row r="68" spans="1:8">
@@ -8841,7 +8841,7 @@
         <v>78.72790000000001</v>
       </c>
       <c r="H68">
-        <v>310.87606</v>
+        <v>310.8760595</v>
       </c>
     </row>
     <row r="69" spans="1:8">
@@ -8867,7 +8867,7 @@
         <v>17.93853</v>
       </c>
       <c r="H69">
-        <v>175.81907</v>
+        <v>175.8190685</v>
       </c>
     </row>
     <row r="70" spans="1:8">
@@ -8893,7 +8893,7 @@
         <v>38.75582</v>
       </c>
       <c r="H70">
-        <v>275.93813</v>
+        <v>275.938135</v>
       </c>
     </row>
     <row r="71" spans="1:8">
@@ -8919,7 +8919,7 @@
         <v>34.61562</v>
       </c>
       <c r="H71">
-        <v>226.60577</v>
+        <v>226.6057699</v>
       </c>
     </row>
     <row r="72" spans="1:8">
@@ -8945,7 +8945,7 @@
         <v>126.30177</v>
       </c>
       <c r="H72">
-        <v>442.53249</v>
+        <v>442.5324941</v>
       </c>
     </row>
     <row r="73" spans="1:8">
@@ -8971,7 +8971,7 @@
         <v>55.13962</v>
       </c>
       <c r="H73">
-        <v>456.00984</v>
+        <v>456.0098384</v>
       </c>
     </row>
     <row r="74" spans="1:8">
@@ -8997,7 +8997,7 @@
         <v>117.18526</v>
       </c>
       <c r="H74">
-        <v>391.14981</v>
+        <v>391.1498103</v>
       </c>
     </row>
     <row r="75" spans="1:8">
@@ -9023,7 +9023,7 @@
         <v>48.61332</v>
       </c>
       <c r="H75">
-        <v>400.36125</v>
+        <v>400.3612517</v>
       </c>
     </row>
     <row r="76" spans="1:8">
@@ -9049,7 +9049,7 @@
         <v>143.77609</v>
       </c>
       <c r="H76">
-        <v>464.5313</v>
+        <v>464.5312972</v>
       </c>
     </row>
     <row r="77" spans="1:8">
@@ -9075,7 +9075,7 @@
         <v>22.69685</v>
       </c>
       <c r="H77">
-        <v>327.0963</v>
+        <v>327.0963013</v>
       </c>
     </row>
     <row r="78" spans="1:8">
@@ -9101,7 +9101,7 @@
         <v>164.73214</v>
       </c>
       <c r="H78">
-        <v>598.8745699999999</v>
+        <v>598.8745728</v>
       </c>
     </row>
     <row r="79" spans="1:8">
@@ -9127,7 +9127,7 @@
         <v>292.60077</v>
       </c>
       <c r="H79">
-        <v>618.12113</v>
+        <v>618.1211332</v>
       </c>
     </row>
     <row r="80" spans="1:8">
@@ -9153,7 +9153,7 @@
         <v>45.99782</v>
       </c>
       <c r="H80">
-        <v>387.24196</v>
+        <v>387.2419581</v>
       </c>
     </row>
     <row r="81" spans="1:8">
@@ -9179,7 +9179,7 @@
         <v>166.96986</v>
       </c>
       <c r="H81">
-        <v>443.92964</v>
+        <v>443.9296426</v>
       </c>
     </row>
     <row r="82" spans="1:8">
@@ -9205,7 +9205,7 @@
         <v>176.31574</v>
       </c>
       <c r="H82">
-        <v>451.76625</v>
+        <v>451.7662486</v>
       </c>
     </row>
     <row r="83" spans="1:8">
@@ -9231,7 +9231,7 @@
         <v>159.95327</v>
       </c>
       <c r="H83">
-        <v>398.63115</v>
+        <v>398.631147</v>
       </c>
     </row>
     <row r="84" spans="1:8">
@@ -9257,7 +9257,7 @@
         <v>173.04531</v>
       </c>
       <c r="H84">
-        <v>442.53366</v>
+        <v>442.5336565</v>
       </c>
     </row>
     <row r="85" spans="1:8">
@@ -9283,7 +9283,7 @@
         <v>134.40846</v>
       </c>
       <c r="H85">
-        <v>433.54921</v>
+        <v>392.2397153</v>
       </c>
     </row>
     <row r="86" spans="1:8">
@@ -9309,7 +9309,7 @@
         <v>75.87094</v>
       </c>
       <c r="H86">
-        <v>234.00056</v>
+        <v>234.0005622</v>
       </c>
     </row>
     <row r="87" spans="1:8">
@@ -9335,7 +9335,7 @@
         <v>259.14572</v>
       </c>
       <c r="H87">
-        <v>464.61777</v>
+        <v>519.9826393</v>
       </c>
     </row>
     <row r="88" spans="1:8">
@@ -9361,7 +9361,7 @@
         <v>222.98802</v>
       </c>
       <c r="H88">
-        <v>566.50364</v>
+        <v>539.6930202</v>
       </c>
     </row>
     <row r="89" spans="1:8">
@@ -9387,7 +9387,7 @@
         <v>124.63799</v>
       </c>
       <c r="H89">
-        <v>584.1173199999999</v>
+        <v>584.1173216</v>
       </c>
     </row>
     <row r="90" spans="1:8">
@@ -9413,7 +9413,7 @@
         <v>160.82732</v>
       </c>
       <c r="H90">
-        <v>665.67515</v>
+        <v>672.6981309</v>
       </c>
     </row>
     <row r="91" spans="1:8">
@@ -9439,7 +9439,7 @@
         <v>153.18052</v>
       </c>
       <c r="H91">
-        <v>408.12528</v>
+        <v>408.1252776</v>
       </c>
     </row>
     <row r="92" spans="1:8">
@@ -9465,7 +9465,7 @@
         <v>104.48239</v>
       </c>
       <c r="H92">
-        <v>473.54501</v>
+        <v>473.5450121</v>
       </c>
     </row>
     <row r="93" spans="1:8">
@@ -9491,7 +9491,7 @@
         <v>47.06105</v>
       </c>
       <c r="H93">
-        <v>201.01381</v>
+        <v>201.0138124</v>
       </c>
     </row>
     <row r="94" spans="1:8">
@@ -9517,7 +9517,7 @@
         <v>15.9557</v>
       </c>
       <c r="H94">
-        <v>263.80968</v>
+        <v>263.8096786</v>
       </c>
     </row>
     <row r="95" spans="1:8">
@@ -9543,7 +9543,7 @@
         <v>153.22559</v>
       </c>
       <c r="H95">
-        <v>410.47438</v>
+        <v>503.7987326</v>
       </c>
     </row>
     <row r="96" spans="1:8">
@@ -9569,7 +9569,7 @@
         <v>176.76041</v>
       </c>
       <c r="H96">
-        <v>732.15246</v>
+        <v>662.418516</v>
       </c>
     </row>
     <row r="97" spans="1:8">
@@ -9595,7 +9595,7 @@
         <v>140.28138</v>
       </c>
       <c r="H97">
-        <v>559.98006</v>
+        <v>559.9800562</v>
       </c>
     </row>
     <row r="98" spans="1:8">
@@ -9621,7 +9621,7 @@
         <v>72.16233</v>
       </c>
       <c r="H98">
-        <v>416.08934</v>
+        <v>416.0893368</v>
       </c>
     </row>
     <row r="99" spans="1:8">
@@ -9647,7 +9647,7 @@
         <v>39.47981</v>
       </c>
       <c r="H99">
-        <v>243.98126</v>
+        <v>243.9812579</v>
       </c>
     </row>
     <row r="100" spans="1:8">
@@ -9673,7 +9673,7 @@
         <v>126.36096</v>
       </c>
       <c r="H100">
-        <v>504.31769</v>
+        <v>430.5152233</v>
       </c>
     </row>
     <row r="101" spans="1:8">
@@ -9699,7 +9699,7 @@
         <v>131.41862</v>
       </c>
       <c r="H101">
-        <v>519.42827</v>
+        <v>519.4282678</v>
       </c>
     </row>
     <row r="102" spans="1:8">
@@ -9725,7 +9725,7 @@
         <v>103.44613</v>
       </c>
       <c r="H102">
-        <v>352.61523</v>
+        <v>352.6152348</v>
       </c>
     </row>
     <row r="103" spans="1:8">
@@ -9751,7 +9751,7 @@
         <v>35.37862</v>
       </c>
       <c r="H103">
-        <v>258.82975</v>
+        <v>258.8297504</v>
       </c>
     </row>
     <row r="104" spans="1:8">
@@ -9777,7 +9777,7 @@
         <v>137.23038</v>
       </c>
       <c r="H104">
-        <v>412.28265</v>
+        <v>412.2826541</v>
       </c>
     </row>
     <row r="105" spans="1:8">
@@ -9803,7 +9803,7 @@
         <v>142.66438</v>
       </c>
       <c r="H105">
-        <v>400.82751</v>
+        <v>400.8275078</v>
       </c>
     </row>
     <row r="106" spans="1:8">
@@ -9829,7 +9829,7 @@
         <v>146.03176</v>
       </c>
       <c r="H106">
-        <v>459.88812</v>
+        <v>459.8881246</v>
       </c>
     </row>
     <row r="107" spans="1:8">
@@ -9855,7 +9855,7 @@
         <v>107.48365</v>
       </c>
       <c r="H107">
-        <v>302.3189</v>
+        <v>302.3188963</v>
       </c>
     </row>
     <row r="108" spans="1:8">
@@ -9881,7 +9881,7 @@
         <v>73.06931</v>
       </c>
       <c r="H108">
-        <v>241.97911</v>
+        <v>241.9791107</v>
       </c>
     </row>
     <row r="109" spans="1:8">
@@ -9907,7 +9907,7 @@
         <v>188.695</v>
       </c>
       <c r="H109">
-        <v>496.20815</v>
+        <v>496.2081543</v>
       </c>
     </row>
     <row r="110" spans="1:8">
@@ -9933,7 +9933,7 @@
         <v>180.75626</v>
       </c>
       <c r="H110">
-        <v>416.34053</v>
+        <v>416.3405335</v>
       </c>
     </row>
     <row r="111" spans="1:8">
@@ -9959,7 +9959,7 @@
         <v>17.15048</v>
       </c>
       <c r="H111">
-        <v>231.5678</v>
+        <v>231.5678005</v>
       </c>
     </row>
     <row r="112" spans="1:8">
@@ -9985,7 +9985,7 @@
         <v>61.97142</v>
       </c>
       <c r="H112">
-        <v>433.38199</v>
+        <v>433.381989</v>
       </c>
     </row>
     <row r="113" spans="1:8">
@@ -10011,7 +10011,7 @@
         <v>51.05219</v>
       </c>
       <c r="H113">
-        <v>266.99505</v>
+        <v>266.9950524</v>
       </c>
     </row>
     <row r="114" spans="1:8">
@@ -10037,7 +10037,7 @@
         <v>58.97259</v>
       </c>
       <c r="H114">
-        <v>415.87607</v>
+        <v>415.8760686</v>
       </c>
     </row>
     <row r="115" spans="1:8">
@@ -10063,7 +10063,7 @@
         <v>80.08543</v>
       </c>
       <c r="H115">
-        <v>302.78652</v>
+        <v>302.7865199</v>
       </c>
     </row>
     <row r="116" spans="1:8">
@@ -10089,7 +10089,7 @@
         <v>12.84</v>
       </c>
       <c r="H116">
-        <v>163.18385</v>
+        <v>163.1838486</v>
       </c>
     </row>
     <row r="117" spans="1:8">
@@ -10115,7 +10115,7 @@
         <v>108.86742</v>
       </c>
       <c r="H117">
-        <v>654.66036</v>
+        <v>654.6603579</v>
       </c>
     </row>
     <row r="118" spans="1:8">
@@ -10141,7 +10141,7 @@
         <v>117.45371</v>
       </c>
       <c r="H118">
-        <v>406.61116</v>
+        <v>406.6111618</v>
       </c>
     </row>
     <row r="119" spans="1:8">
@@ -10167,7 +10167,7 @@
         <v>58.38769</v>
       </c>
       <c r="H119">
-        <v>213.29919</v>
+        <v>213.2991857</v>
       </c>
     </row>
     <row r="120" spans="1:8">
@@ -10193,7 +10193,7 @@
         <v>24.89203</v>
       </c>
       <c r="H120">
-        <v>184.38142</v>
+        <v>184.3814207</v>
       </c>
     </row>
     <row r="121" spans="1:8">
@@ -10219,7 +10219,7 @@
         <v>126.13824</v>
       </c>
       <c r="H121">
-        <v>697.65052</v>
+        <v>697.6505161</v>
       </c>
     </row>
     <row r="122" spans="1:8">
@@ -10245,7 +10245,7 @@
         <v>43.12722</v>
       </c>
       <c r="H122">
-        <v>382.25181</v>
+        <v>382.251814</v>
       </c>
     </row>
     <row r="123" spans="1:8">
@@ -10271,7 +10271,7 @@
         <v>71.7367</v>
       </c>
       <c r="H123">
-        <v>403.52566</v>
+        <v>403.5256634</v>
       </c>
     </row>
     <row r="124" spans="1:8">
@@ -10297,7 +10297,7 @@
         <v>89.95589</v>
       </c>
       <c r="H124">
-        <v>524.1706799999999</v>
+        <v>524.1706775</v>
       </c>
     </row>
     <row r="125" spans="1:8">
@@ -10323,7 +10323,7 @@
         <v>33.33547</v>
       </c>
       <c r="H125">
-        <v>299.25717</v>
+        <v>299.2571701</v>
       </c>
     </row>
     <row r="126" spans="1:8">
@@ -10349,7 +10349,7 @@
         <v>48.86884</v>
       </c>
       <c r="H126">
-        <v>245.19055</v>
+        <v>245.1905453</v>
       </c>
     </row>
     <row r="127" spans="1:8">
@@ -10375,7 +10375,7 @@
         <v>28.25686</v>
       </c>
       <c r="H127">
-        <v>287.88556</v>
+        <v>287.8855569</v>
       </c>
     </row>
     <row r="128" spans="1:8">
@@ -10401,7 +10401,7 @@
         <v>33.55981</v>
       </c>
       <c r="H128">
-        <v>254.38536</v>
+        <v>254.3853633</v>
       </c>
     </row>
     <row r="129" spans="1:8">
@@ -10427,7 +10427,7 @@
         <v>156.69927</v>
       </c>
       <c r="H129">
-        <v>378.19678</v>
+        <v>378.196776</v>
       </c>
     </row>
     <row r="130" spans="1:8">
@@ -10453,7 +10453,7 @@
         <v>22.64148</v>
       </c>
       <c r="H130">
-        <v>460.83522</v>
+        <v>460.835222</v>
       </c>
     </row>
     <row r="131" spans="1:8">
@@ -10479,7 +10479,7 @@
         <v>121.64896</v>
       </c>
       <c r="H131">
-        <v>662.50869</v>
+        <v>662.5086856</v>
       </c>
     </row>
     <row r="132" spans="1:8">
@@ -10505,7 +10505,7 @@
         <v>130.96401</v>
       </c>
       <c r="H132">
-        <v>416.57487</v>
+        <v>416.5748672</v>
       </c>
     </row>
     <row r="133" spans="1:8">
@@ -10531,7 +10531,7 @@
         <v>6.61557</v>
       </c>
       <c r="H133">
-        <v>149.96625</v>
+        <v>149.9662518</v>
       </c>
     </row>
     <row r="134" spans="1:8">
@@ -10557,7 +10557,7 @@
         <v>114.94331</v>
       </c>
       <c r="H134">
-        <v>428.38852</v>
+        <v>428.3885239</v>
       </c>
     </row>
     <row r="135" spans="1:8">
@@ -10583,7 +10583,7 @@
         <v>40.28732</v>
       </c>
       <c r="H135">
-        <v>383.99825</v>
+        <v>383.9982453</v>
       </c>
     </row>
     <row r="136" spans="1:8">
@@ -10609,7 +10609,7 @@
         <v>99.39731999999999</v>
       </c>
       <c r="H136">
-        <v>264.14954</v>
+        <v>264.1495432</v>
       </c>
     </row>
     <row r="137" spans="1:8">
@@ -10635,7 +10635,7 @@
         <v>42.33115</v>
       </c>
       <c r="H137">
-        <v>217.86276</v>
+        <v>217.8627579</v>
       </c>
     </row>
     <row r="138" spans="1:8">
@@ -10661,7 +10661,7 @@
         <v>97.87236</v>
       </c>
       <c r="H138">
-        <v>331.10138</v>
+        <v>331.101377</v>
       </c>
     </row>
     <row r="139" spans="1:8">
@@ -10687,7 +10687,7 @@
         <v>172.7581</v>
       </c>
       <c r="H139">
-        <v>487.22321</v>
+        <v>487.223207</v>
       </c>
     </row>
     <row r="140" spans="1:8">
@@ -10713,7 +10713,7 @@
         <v>114.34975</v>
       </c>
       <c r="H140">
-        <v>341.67541</v>
+        <v>338.9028211</v>
       </c>
     </row>
     <row r="141" spans="1:8">
@@ -10739,7 +10739,7 @@
         <v>105.81984</v>
       </c>
       <c r="H141">
-        <v>307.13456</v>
+        <v>307.1345637</v>
       </c>
     </row>
     <row r="142" spans="1:8">
@@ -10765,7 +10765,7 @@
         <v>186.39456</v>
       </c>
       <c r="H142">
-        <v>488.8716</v>
+        <v>505.2381855</v>
       </c>
     </row>
     <row r="143" spans="1:8">
@@ -10791,7 +10791,7 @@
         <v>64.6742</v>
       </c>
       <c r="H143">
-        <v>215.96173</v>
+        <v>215.9617303</v>
       </c>
     </row>
     <row r="144" spans="1:8">
@@ -10817,7 +10817,7 @@
         <v>230.79218</v>
       </c>
       <c r="H144">
-        <v>416.0812</v>
+        <v>458.816788</v>
       </c>
     </row>
     <row r="145" spans="1:8">
@@ -10843,7 +10843,7 @@
         <v>50.56607</v>
       </c>
       <c r="H145">
-        <v>360.9039</v>
+        <v>360.9039045</v>
       </c>
     </row>
     <row r="146" spans="1:8">
@@ -10869,7 +10869,7 @@
         <v>31.27628</v>
       </c>
       <c r="H146">
-        <v>181.15579</v>
+        <v>181.1557851</v>
       </c>
     </row>
     <row r="147" spans="1:8">
@@ -10895,7 +10895,7 @@
         <v>33.63228</v>
       </c>
       <c r="H147">
-        <v>230.08616</v>
+        <v>230.0861579</v>
       </c>
     </row>
     <row r="148" spans="1:8">
@@ -10921,7 +10921,7 @@
         <v>154.49544</v>
       </c>
       <c r="H148">
-        <v>481.56003</v>
+        <v>481.5600304</v>
       </c>
     </row>
     <row r="149" spans="1:8">
@@ -10947,7 +10947,7 @@
         <v>37.75315</v>
       </c>
       <c r="H149">
-        <v>206.30787</v>
+        <v>249.3338416</v>
       </c>
     </row>
     <row r="150" spans="1:8">
@@ -10973,7 +10973,7 @@
         <v>100.54971</v>
       </c>
       <c r="H150">
-        <v>515.32259</v>
+        <v>515.3225858</v>
       </c>
     </row>
     <row r="151" spans="1:8">
@@ -10999,7 +10999,7 @@
         <v>132.9646</v>
       </c>
       <c r="H151">
-        <v>773.792</v>
+        <v>773.7919993</v>
       </c>
     </row>
     <row r="152" spans="1:8">
@@ -11025,7 +11025,7 @@
         <v>36.99724</v>
       </c>
       <c r="H152">
-        <v>322.44541</v>
+        <v>322.445409</v>
       </c>
     </row>
     <row r="153" spans="1:8">
@@ -11051,7 +11051,7 @@
         <v>269.22051</v>
       </c>
       <c r="H153">
-        <v>980.4624700000001</v>
+        <v>980.4624665</v>
       </c>
     </row>
     <row r="154" spans="1:8">
@@ -11077,7 +11077,7 @@
         <v>125.78401</v>
       </c>
       <c r="H154">
-        <v>567.81628</v>
+        <v>566.4730823</v>
       </c>
     </row>
     <row r="155" spans="1:8">
@@ -11103,7 +11103,7 @@
         <v>139.55193</v>
       </c>
       <c r="H155">
-        <v>614.45406</v>
+        <v>596.1440229</v>
       </c>
     </row>
     <row r="156" spans="1:8">
@@ -11129,7 +11129,7 @@
         <v>208.23608</v>
       </c>
       <c r="H156">
-        <v>671.51953</v>
+        <v>671.5195297</v>
       </c>
     </row>
     <row r="157" spans="1:8">
@@ -11155,7 +11155,7 @@
         <v>197.28716</v>
       </c>
       <c r="H157">
-        <v>539.0311799999999</v>
+        <v>539.0311789</v>
       </c>
     </row>
     <row r="158" spans="1:8">
@@ -11181,7 +11181,7 @@
         <v>256.32196</v>
       </c>
       <c r="H158">
-        <v>747.32823</v>
+        <v>747.3282349</v>
       </c>
     </row>
     <row r="159" spans="1:8">
@@ -11207,7 +11207,7 @@
         <v>214.6788</v>
       </c>
       <c r="H159">
-        <v>609.39451</v>
+        <v>609.3945122</v>
       </c>
     </row>
     <row r="160" spans="1:8">
@@ -11233,7 +11233,7 @@
         <v>91.17872</v>
       </c>
       <c r="H160">
-        <v>327.79727</v>
+        <v>327.797273</v>
       </c>
     </row>
     <row r="161" spans="1:8">
@@ -11259,7 +11259,7 @@
         <v>93.75266000000001</v>
       </c>
       <c r="H161">
-        <v>298.05156</v>
+        <v>270.614609</v>
       </c>
     </row>
     <row r="162" spans="1:8">
@@ -11285,7 +11285,7 @@
         <v>125.07838</v>
       </c>
       <c r="H162">
-        <v>346.11069</v>
+        <v>346.1106872</v>
       </c>
     </row>
     <row r="163" spans="1:8">
@@ -11311,7 +11311,7 @@
         <v>53.89212</v>
       </c>
       <c r="H163">
-        <v>294.35626</v>
+        <v>294.356261</v>
       </c>
     </row>
     <row r="164" spans="1:8">
@@ -11337,7 +11337,7 @@
         <v>85.842</v>
       </c>
       <c r="H164">
-        <v>406.21122</v>
+        <v>406.2112233</v>
       </c>
     </row>
     <row r="165" spans="1:8">
@@ -11363,7 +11363,7 @@
         <v>151.70627</v>
       </c>
       <c r="H165">
-        <v>427.81132</v>
+        <v>427.8113223</v>
       </c>
     </row>
     <row r="166" spans="1:8">
@@ -11389,7 +11389,7 @@
         <v>359.86533</v>
       </c>
       <c r="H166">
-        <v>1037.91891</v>
+        <v>1037.918909</v>
       </c>
     </row>
     <row r="167" spans="1:8">
@@ -11415,7 +11415,7 @@
         <v>80.16845000000001</v>
       </c>
       <c r="H167">
-        <v>315.27003</v>
+        <v>315.2700298</v>
       </c>
     </row>
     <row r="168" spans="1:8">
@@ -11441,7 +11441,7 @@
         <v>20.49559</v>
       </c>
       <c r="H168">
-        <v>156.28119</v>
+        <v>156.2811915</v>
       </c>
     </row>
     <row r="169" spans="1:8">
@@ -11467,7 +11467,7 @@
         <v>27.20203</v>
       </c>
       <c r="H169">
-        <v>193.95168</v>
+        <v>193.9516805</v>
       </c>
     </row>
     <row r="170" spans="1:8">
@@ -11493,7 +11493,7 @@
         <v>74.46101</v>
       </c>
       <c r="H170">
-        <v>404.06933</v>
+        <v>404.0693274</v>
       </c>
     </row>
     <row r="171" spans="1:8">
@@ -11519,7 +11519,7 @@
         <v>14.9422</v>
       </c>
       <c r="H171">
-        <v>164.61566</v>
+        <v>164.6156592</v>
       </c>
     </row>
     <row r="172" spans="1:8">
@@ -11545,7 +11545,7 @@
         <v>23.33923</v>
       </c>
       <c r="H172">
-        <v>143.95107</v>
+        <v>143.9510691</v>
       </c>
     </row>
     <row r="173" spans="1:8">
@@ -11571,7 +11571,7 @@
         <v>40.88584</v>
       </c>
       <c r="H173">
-        <v>329.79033</v>
+        <v>329.7903329</v>
       </c>
     </row>
     <row r="174" spans="1:8">
@@ -11597,7 +11597,7 @@
         <v>158.46818</v>
       </c>
       <c r="H174">
-        <v>400.38983</v>
+        <v>402.7898018</v>
       </c>
     </row>
     <row r="175" spans="1:8">
@@ -11623,7 +11623,7 @@
         <v>202.43131</v>
       </c>
       <c r="H175">
-        <v>518.98277</v>
+        <v>467.6259934</v>
       </c>
     </row>
     <row r="176" spans="1:8">
@@ -11649,7 +11649,7 @@
         <v>50.07727</v>
       </c>
       <c r="H176">
-        <v>356.9194</v>
+        <v>356.9194044</v>
       </c>
     </row>
     <row r="177" spans="1:8">
@@ -11675,7 +11675,7 @@
         <v>69.10391</v>
       </c>
       <c r="H177">
-        <v>340.88059</v>
+        <v>340.8805912</v>
       </c>
     </row>
     <row r="178" spans="1:8">
@@ -11701,7 +11701,7 @@
         <v>22.1557</v>
       </c>
       <c r="H178">
-        <v>251.15045</v>
+        <v>251.1504532</v>
       </c>
     </row>
     <row r="179" spans="1:8">
@@ -11727,7 +11727,7 @@
         <v>45.0925</v>
       </c>
       <c r="H179">
-        <v>394.51341</v>
+        <v>394.5134096</v>
       </c>
     </row>
     <row r="180" spans="1:8">
@@ -11753,7 +11753,7 @@
         <v>161.61194</v>
       </c>
       <c r="H180">
-        <v>677.76268</v>
+        <v>619.4910965</v>
       </c>
     </row>
     <row r="181" spans="1:8">
@@ -11779,7 +11779,7 @@
         <v>146.89709</v>
       </c>
       <c r="H181">
-        <v>645.06861</v>
+        <v>645.0686088</v>
       </c>
     </row>
     <row r="182" spans="1:8">
@@ -11805,7 +11805,7 @@
         <v>185.17954</v>
       </c>
       <c r="H182">
-        <v>732.69102</v>
+        <v>651.7687837</v>
       </c>
     </row>
     <row r="183" spans="1:8">
@@ -11831,7 +11831,7 @@
         <v>198.23787</v>
       </c>
       <c r="H183">
-        <v>660.08215</v>
+        <v>660.0821526</v>
       </c>
     </row>
     <row r="184" spans="1:8">
@@ -11857,7 +11857,7 @@
         <v>133.26638</v>
       </c>
       <c r="H184">
-        <v>373.47882</v>
+        <v>373.4788228</v>
       </c>
     </row>
     <row r="185" spans="1:8">
@@ -11883,7 +11883,7 @@
         <v>78.42586</v>
       </c>
       <c r="H185">
-        <v>497.02649</v>
+        <v>497.0264943</v>
       </c>
     </row>
     <row r="186" spans="1:8">
@@ -11909,7 +11909,7 @@
         <v>52.3657</v>
       </c>
       <c r="H186">
-        <v>254.66766</v>
+        <v>254.6676628</v>
       </c>
     </row>
     <row r="187" spans="1:8">
@@ -11935,7 +11935,7 @@
         <v>165.53184</v>
       </c>
       <c r="H187">
-        <v>407.15618</v>
+        <v>408.5212341</v>
       </c>
     </row>
     <row r="188" spans="1:8">
@@ -11961,7 +11961,7 @@
         <v>34.08714</v>
       </c>
       <c r="H188">
-        <v>247.5099</v>
+        <v>247.5099011</v>
       </c>
     </row>
     <row r="189" spans="1:8">
@@ -11987,7 +11987,7 @@
         <v>275.86695</v>
       </c>
       <c r="H189">
-        <v>597.15745</v>
+        <v>614.8593912</v>
       </c>
     </row>
     <row r="190" spans="1:8">
@@ -12013,7 +12013,7 @@
         <v>210.15742</v>
       </c>
       <c r="H190">
-        <v>511.94547</v>
+        <v>514.3132782</v>
       </c>
     </row>
     <row r="191" spans="1:8">
@@ -12039,7 +12039,7 @@
         <v>63.24535</v>
       </c>
       <c r="H191">
-        <v>396.4881</v>
+        <v>396.4880984</v>
       </c>
     </row>
     <row r="192" spans="1:8">
@@ -12065,7 +12065,7 @@
         <v>66.02652999999999</v>
       </c>
       <c r="H192">
-        <v>360.42765</v>
+        <v>360.4276505</v>
       </c>
     </row>
     <row r="193" spans="1:8">
@@ -12091,7 +12091,7 @@
         <v>204.96594</v>
       </c>
       <c r="H193">
-        <v>603.12818</v>
+        <v>603.1281766</v>
       </c>
     </row>
     <row r="194" spans="1:8">
@@ -12117,7 +12117,7 @@
         <v>190.23071</v>
       </c>
       <c r="H194">
-        <v>483.16064</v>
+        <v>430.1358058</v>
       </c>
     </row>
     <row r="195" spans="1:8">
@@ -12143,7 +12143,7 @@
         <v>127.19558</v>
       </c>
       <c r="H195">
-        <v>416.66931</v>
+        <v>376.16297</v>
       </c>
     </row>
     <row r="196" spans="1:8">
@@ -12169,7 +12169,7 @@
         <v>209.27052</v>
       </c>
       <c r="H196">
-        <v>541.31694</v>
+        <v>465.1407407</v>
       </c>
     </row>
     <row r="197" spans="1:8">
@@ -12195,7 +12195,7 @@
         <v>182.2491</v>
       </c>
       <c r="H197">
-        <v>410.65009</v>
+        <v>410.6500929</v>
       </c>
     </row>
     <row r="198" spans="1:8">
@@ -12221,7 +12221,7 @@
         <v>172.10128</v>
       </c>
       <c r="H198">
-        <v>397.94964</v>
+        <v>397.9496391</v>
       </c>
     </row>
     <row r="199" spans="1:8">
@@ -12247,7 +12247,7 @@
         <v>231.57743</v>
       </c>
       <c r="H199">
-        <v>482.52012</v>
+        <v>473.4896188</v>
       </c>
     </row>
     <row r="200" spans="1:8">
@@ -12273,7 +12273,7 @@
         <v>130.03147</v>
       </c>
       <c r="H200">
-        <v>348.07997</v>
+        <v>342.1642633</v>
       </c>
     </row>
     <row r="201" spans="1:8">
@@ -12299,7 +12299,7 @@
         <v>187.00986</v>
       </c>
       <c r="H201">
-        <v>483.65913</v>
+        <v>483.6591283</v>
       </c>
     </row>
     <row r="202" spans="1:8">
@@ -12325,7 +12325,7 @@
         <v>23.58945</v>
       </c>
       <c r="H202">
-        <v>147.70885</v>
+        <v>147.7088483</v>
       </c>
     </row>
     <row r="203" spans="1:8">
@@ -12351,7 +12351,7 @@
         <v>37.6896</v>
       </c>
       <c r="H203">
-        <v>202.75855</v>
+        <v>202.7585532</v>
       </c>
     </row>
     <row r="204" spans="1:8">
@@ -12377,7 +12377,7 @@
         <v>85.53915000000001</v>
       </c>
       <c r="H204">
-        <v>431.76754</v>
+        <v>431.7675416</v>
       </c>
     </row>
     <row r="205" spans="1:8">
@@ -12403,7 +12403,7 @@
         <v>28.14896</v>
       </c>
       <c r="H205">
-        <v>132.71694</v>
+        <v>132.716937</v>
       </c>
     </row>
     <row r="206" spans="1:8">
@@ -12429,7 +12429,7 @@
         <v>47.33992</v>
       </c>
       <c r="H206">
-        <v>184.3604</v>
+        <v>184.3604036</v>
       </c>
     </row>
     <row r="207" spans="1:8">
@@ -12455,7 +12455,7 @@
         <v>183.845</v>
       </c>
       <c r="H207">
-        <v>436.34386</v>
+        <v>436.3438558</v>
       </c>
     </row>
     <row r="208" spans="1:8">
@@ -12481,7 +12481,7 @@
         <v>80.74884</v>
       </c>
       <c r="H208">
-        <v>465.29092</v>
+        <v>465.2909158</v>
       </c>
     </row>
     <row r="209" spans="1:8">
@@ -12507,7 +12507,7 @@
         <v>68.57881999999999</v>
       </c>
       <c r="H209">
-        <v>346.76661</v>
+        <v>346.7666105</v>
       </c>
     </row>
     <row r="210" spans="1:8">
@@ -12533,7 +12533,7 @@
         <v>54.9716</v>
       </c>
       <c r="H210">
-        <v>284.54538</v>
+        <v>284.5453824</v>
       </c>
     </row>
     <row r="211" spans="1:8">
@@ -12559,7 +12559,7 @@
         <v>90.05163</v>
       </c>
       <c r="H211">
-        <v>319.39143</v>
+        <v>319.3914306</v>
       </c>
     </row>
     <row r="212" spans="1:8">
@@ -12585,7 +12585,7 @@
         <v>87.87008</v>
       </c>
       <c r="H212">
-        <v>316.53334</v>
+        <v>342.1767368</v>
       </c>
     </row>
     <row r="213" spans="1:8">
@@ -12611,7 +12611,7 @@
         <v>28.4472</v>
       </c>
       <c r="H213">
-        <v>153.80574</v>
+        <v>153.8057437</v>
       </c>
     </row>
     <row r="214" spans="1:8">
@@ -12637,7 +12637,7 @@
         <v>17.81061</v>
       </c>
       <c r="H214">
-        <v>139.97326</v>
+        <v>139.973256</v>
       </c>
     </row>
     <row r="215" spans="1:8">
@@ -12663,7 +12663,7 @@
         <v>31.97125</v>
       </c>
       <c r="H215">
-        <v>200.66885</v>
+        <v>200.6688455</v>
       </c>
     </row>
     <row r="216" spans="1:8">
@@ -12689,7 +12689,7 @@
         <v>44.15774</v>
       </c>
       <c r="H216">
-        <v>298.72261</v>
+        <v>298.7226066</v>
       </c>
     </row>
     <row r="217" spans="1:8">
@@ -12715,7 +12715,7 @@
         <v>110.69995</v>
       </c>
       <c r="H217">
-        <v>635.81873</v>
+        <v>635.8187304</v>
       </c>
     </row>
     <row r="218" spans="1:8">
@@ -12741,7 +12741,7 @@
         <v>118.62286</v>
       </c>
       <c r="H218">
-        <v>596.79362</v>
+        <v>596.7936184</v>
       </c>
     </row>
     <row r="219" spans="1:8">
@@ -12767,7 +12767,7 @@
         <v>97.50071</v>
       </c>
       <c r="H219">
-        <v>465.95966</v>
+        <v>465.9596618</v>
       </c>
     </row>
     <row r="220" spans="1:8">
@@ -12793,7 +12793,7 @@
         <v>188.33086</v>
       </c>
       <c r="H220">
-        <v>660.38933</v>
+        <v>660.3893345</v>
       </c>
     </row>
     <row r="221" spans="1:8">
@@ -12819,7 +12819,7 @@
         <v>32.90166</v>
       </c>
       <c r="H221">
-        <v>174.494</v>
+        <v>174.4939971</v>
       </c>
     </row>
     <row r="222" spans="1:8">
@@ -12845,7 +12845,7 @@
         <v>164.39624</v>
       </c>
       <c r="H222">
-        <v>363.49372</v>
+        <v>363.4937157</v>
       </c>
     </row>
     <row r="223" spans="1:8">
@@ -12871,7 +12871,7 @@
         <v>56.82442</v>
       </c>
       <c r="H223">
-        <v>222.7744</v>
+        <v>222.7744009</v>
       </c>
     </row>
     <row r="224" spans="1:8">
@@ -12897,7 +12897,7 @@
         <v>42.22353</v>
       </c>
       <c r="H224">
-        <v>327.2489</v>
+        <v>412.4948274</v>
       </c>
     </row>
     <row r="225" spans="1:8">
@@ -12923,7 +12923,7 @@
         <v>300.15041</v>
       </c>
       <c r="H225">
-        <v>699.5992199999999</v>
+        <v>631.7530484</v>
       </c>
     </row>
     <row r="226" spans="1:8">
@@ -12949,7 +12949,7 @@
         <v>159.70185</v>
       </c>
       <c r="H226">
-        <v>521.5493300000001</v>
+        <v>521.5493276</v>
       </c>
     </row>
     <row r="227" spans="1:8">
@@ -12975,7 +12975,7 @@
         <v>130.62585</v>
       </c>
       <c r="H227">
-        <v>379.38508</v>
+        <v>379.385083</v>
       </c>
     </row>
     <row r="228" spans="1:8">
@@ -13001,7 +13001,7 @@
         <v>189.80018</v>
       </c>
       <c r="H228">
-        <v>372.26776</v>
+        <v>446.943946</v>
       </c>
     </row>
     <row r="229" spans="1:8">
@@ -13027,7 +13027,7 @@
         <v>105.81982</v>
       </c>
       <c r="H229">
-        <v>342.29191</v>
+        <v>342.2919076</v>
       </c>
     </row>
     <row r="230" spans="1:8">
@@ -13053,7 +13053,7 @@
         <v>107.07185</v>
       </c>
       <c r="H230">
-        <v>351.77214</v>
+        <v>351.7721408</v>
       </c>
     </row>
     <row r="231" spans="1:8">
@@ -13079,7 +13079,7 @@
         <v>94.2496</v>
       </c>
       <c r="H231">
-        <v>368.04839</v>
+        <v>368.0483902</v>
       </c>
     </row>
     <row r="232" spans="1:8">
@@ -13105,7 +13105,7 @@
         <v>102.49639</v>
       </c>
       <c r="H232">
-        <v>425.08909</v>
+        <v>425.089087</v>
       </c>
     </row>
     <row r="233" spans="1:8">
@@ -13131,7 +13131,7 @@
         <v>186.73866</v>
       </c>
       <c r="H233">
-        <v>388.60515</v>
+        <v>388.605148</v>
       </c>
     </row>
     <row r="234" spans="1:8">
@@ -13157,7 +13157,7 @@
         <v>303.57355</v>
       </c>
       <c r="H234">
-        <v>544.19811</v>
+        <v>544.198112</v>
       </c>
     </row>
     <row r="235" spans="1:8">
@@ -13183,7 +13183,7 @@
         <v>109.54093</v>
       </c>
       <c r="H235">
-        <v>312.59741</v>
+        <v>312.5974101</v>
       </c>
     </row>
     <row r="236" spans="1:8">
@@ -13235,7 +13235,7 @@
         <v>132.96888</v>
       </c>
       <c r="H237">
-        <v>633.15778</v>
+        <v>633.1577841</v>
       </c>
     </row>
     <row r="238" spans="1:8">
@@ -13261,7 +13261,7 @@
         <v>31.27803</v>
       </c>
       <c r="H238">
-        <v>205.04758</v>
+        <v>205.0475832</v>
       </c>
     </row>
     <row r="239" spans="1:8">
@@ -13287,7 +13287,7 @@
         <v>149.99942</v>
       </c>
       <c r="H239">
-        <v>424.66194</v>
+        <v>424.661938</v>
       </c>
     </row>
     <row r="240" spans="1:8">
@@ -13313,7 +13313,7 @@
         <v>56.2432</v>
       </c>
       <c r="H240">
-        <v>411.3674</v>
+        <v>411.3673962</v>
       </c>
     </row>
     <row r="241" spans="1:8">
@@ -13339,7 +13339,7 @@
         <v>54.7859</v>
       </c>
       <c r="H241">
-        <v>360.53038</v>
+        <v>360.5303819</v>
       </c>
     </row>
     <row r="242" spans="1:8">
@@ -13365,7 +13365,7 @@
         <v>100.77033</v>
       </c>
       <c r="H242">
-        <v>324.84195</v>
+        <v>324.8419476</v>
       </c>
     </row>
     <row r="243" spans="1:8">
@@ -13391,7 +13391,7 @@
         <v>113.37216</v>
       </c>
       <c r="H243">
-        <v>328.58432</v>
+        <v>328.5843234</v>
       </c>
     </row>
     <row r="244" spans="1:8">
@@ -13417,7 +13417,7 @@
         <v>47.25156</v>
       </c>
       <c r="H244">
-        <v>264.40576</v>
+        <v>264.4057576</v>
       </c>
     </row>
     <row r="245" spans="1:8">
@@ -13443,7 +13443,7 @@
         <v>112.95585</v>
       </c>
       <c r="H245">
-        <v>458.97016</v>
+        <v>458.9701574</v>
       </c>
     </row>
     <row r="246" spans="1:8">
@@ -13469,7 +13469,7 @@
         <v>93.22074000000001</v>
       </c>
       <c r="H246">
-        <v>339.16766</v>
+        <v>339.1676604</v>
       </c>
     </row>
     <row r="247" spans="1:8">
@@ -13495,7 +13495,7 @@
         <v>74.1228</v>
       </c>
       <c r="H247">
-        <v>287.59846</v>
+        <v>287.5984632</v>
       </c>
     </row>
     <row r="248" spans="1:8">
@@ -13521,7 +13521,7 @@
         <v>56.00488</v>
       </c>
       <c r="H248">
-        <v>243.5017</v>
+        <v>243.5016992</v>
       </c>
     </row>
     <row r="249" spans="1:8">
@@ -13547,7 +13547,7 @@
         <v>19.75974</v>
       </c>
       <c r="H249">
-        <v>119.8461</v>
+        <v>119.8461025</v>
       </c>
     </row>
     <row r="250" spans="1:8">
@@ -13573,7 +13573,7 @@
         <v>136.30881</v>
       </c>
       <c r="H250">
-        <v>428.07631</v>
+        <v>428.0763111</v>
       </c>
     </row>
     <row r="251" spans="1:8">
@@ -13599,7 +13599,7 @@
         <v>141.08724</v>
       </c>
       <c r="H251">
-        <v>409.68456</v>
+        <v>409.6845613</v>
       </c>
     </row>
     <row r="252" spans="1:8">
@@ -13625,7 +13625,7 @@
         <v>25.41144</v>
       </c>
       <c r="H252">
-        <v>214.52466</v>
+        <v>214.5246586</v>
       </c>
     </row>
     <row r="253" spans="1:8">
@@ -13651,7 +13651,7 @@
         <v>53.19544</v>
       </c>
       <c r="H253">
-        <v>231.24389</v>
+        <v>231.2438858</v>
       </c>
     </row>
     <row r="254" spans="1:8">
@@ -13677,7 +13677,7 @@
         <v>70.41243</v>
       </c>
       <c r="H254">
-        <v>361.69066</v>
+        <v>361.6906595</v>
       </c>
     </row>
     <row r="255" spans="1:8">
@@ -13703,7 +13703,7 @@
         <v>204.45631</v>
       </c>
       <c r="H255">
-        <v>486.22486</v>
+        <v>486.224865</v>
       </c>
     </row>
     <row r="256" spans="1:8">
@@ -13729,7 +13729,7 @@
         <v>136.46653</v>
       </c>
       <c r="H256">
-        <v>701.61241</v>
+        <v>701.6124105</v>
       </c>
     </row>
     <row r="257" spans="1:8">
@@ -13755,7 +13755,7 @@
         <v>78.97882</v>
       </c>
       <c r="H257">
-        <v>539.02065</v>
+        <v>539.0206473</v>
       </c>
     </row>
     <row r="258" spans="1:8">
@@ -13781,7 +13781,7 @@
         <v>131.11648</v>
       </c>
       <c r="H258">
-        <v>356.18885</v>
+        <v>362.4138017</v>
       </c>
     </row>
     <row r="259" spans="1:8">
@@ -13807,7 +13807,7 @@
         <v>156.17679</v>
       </c>
       <c r="H259">
-        <v>361.27138</v>
+        <v>361.2713832</v>
       </c>
     </row>
     <row r="260" spans="1:8">
@@ -13833,7 +13833,7 @@
         <v>202.45341</v>
       </c>
       <c r="H260">
-        <v>455.31311</v>
+        <v>455.3131114</v>
       </c>
     </row>
     <row r="261" spans="1:8">
@@ -13859,7 +13859,7 @@
         <v>137.85836</v>
       </c>
       <c r="H261">
-        <v>505.61707</v>
+        <v>505.617073</v>
       </c>
     </row>
     <row r="262" spans="1:8">
@@ -13885,7 +13885,7 @@
         <v>131.37635</v>
       </c>
       <c r="H262">
-        <v>466.89073</v>
+        <v>553.3193418</v>
       </c>
     </row>
     <row r="263" spans="1:8">
@@ -13911,7 +13911,7 @@
         <v>56.00156</v>
       </c>
       <c r="H263">
-        <v>300.54449</v>
+        <v>300.5444935</v>
       </c>
     </row>
     <row r="264" spans="1:8">
@@ -13937,7 +13937,7 @@
         <v>76.18266</v>
       </c>
       <c r="H264">
-        <v>344.19304</v>
+        <v>344.1930431</v>
       </c>
     </row>
     <row r="265" spans="1:8">
@@ -13963,7 +13963,7 @@
         <v>223.81361</v>
       </c>
       <c r="H265">
-        <v>510.51728</v>
+        <v>510.517279</v>
       </c>
     </row>
     <row r="266" spans="1:8">
@@ -13989,7 +13989,7 @@
         <v>65.42834999999999</v>
       </c>
       <c r="H266">
-        <v>262.44374</v>
+        <v>262.4437391</v>
       </c>
     </row>
     <row r="267" spans="1:8">
@@ -14015,7 +14015,7 @@
         <v>128.05582</v>
       </c>
       <c r="H267">
-        <v>408.16044</v>
+        <v>408.1604442</v>
       </c>
     </row>
     <row r="268" spans="1:8">
@@ -14041,7 +14041,7 @@
         <v>27.99498</v>
       </c>
       <c r="H268">
-        <v>201.01575</v>
+        <v>201.0157455</v>
       </c>
     </row>
     <row r="269" spans="1:8">
@@ -14067,7 +14067,7 @@
         <v>26.37397</v>
       </c>
       <c r="H269">
-        <v>233.94169</v>
+        <v>233.941688</v>
       </c>
     </row>
     <row r="270" spans="1:8">
@@ -14093,7 +14093,7 @@
         <v>26.84365</v>
       </c>
       <c r="H270">
-        <v>218.97252</v>
+        <v>218.9725157</v>
       </c>
     </row>
     <row r="271" spans="1:8">
@@ -14119,7 +14119,7 @@
         <v>26.85293</v>
       </c>
       <c r="H271">
-        <v>193.26321</v>
+        <v>193.2632131</v>
       </c>
     </row>
     <row r="272" spans="1:8">
@@ -14145,7 +14145,7 @@
         <v>217.14365</v>
       </c>
       <c r="H272">
-        <v>550.9025</v>
+        <v>550.9025028</v>
       </c>
     </row>
     <row r="273" spans="1:8">
@@ -14171,7 +14171,7 @@
         <v>128.3185</v>
       </c>
       <c r="H273">
-        <v>353.36176</v>
+        <v>353.3617624</v>
       </c>
     </row>
     <row r="274" spans="1:8">
@@ -14197,7 +14197,7 @@
         <v>162.68694</v>
       </c>
       <c r="H274">
-        <v>425.92841</v>
+        <v>425.928408</v>
       </c>
     </row>
     <row r="275" spans="1:8">
@@ -14223,7 +14223,7 @@
         <v>185.38914</v>
       </c>
       <c r="H275">
-        <v>681.07791</v>
+        <v>638.6166702</v>
       </c>
     </row>
     <row r="276" spans="1:8">
@@ -14249,7 +14249,7 @@
         <v>34.20095</v>
       </c>
       <c r="H276">
-        <v>262.01286</v>
+        <v>262.0128642</v>
       </c>
     </row>
     <row r="277" spans="1:8">
@@ -14275,7 +14275,7 @@
         <v>4.36766</v>
       </c>
       <c r="H277">
-        <v>119.27237</v>
+        <v>119.2723725</v>
       </c>
     </row>
     <row r="278" spans="1:8">
@@ -14301,7 +14301,7 @@
         <v>33.81692</v>
       </c>
       <c r="H278">
-        <v>155.88119</v>
+        <v>155.881187</v>
       </c>
     </row>
     <row r="279" spans="1:8">
@@ -14327,7 +14327,7 @@
         <v>100.20009</v>
       </c>
       <c r="H279">
-        <v>324.60411</v>
+        <v>324.6041146</v>
       </c>
     </row>
     <row r="280" spans="1:8">
@@ -14353,7 +14353,7 @@
         <v>93.97591</v>
       </c>
       <c r="H280">
-        <v>390.57048</v>
+        <v>390.5704811</v>
       </c>
     </row>
     <row r="281" spans="1:8">
@@ -14379,7 +14379,7 @@
         <v>40.91006</v>
       </c>
       <c r="H281">
-        <v>240.91086</v>
+        <v>240.9108572</v>
       </c>
     </row>
     <row r="282" spans="1:8">
@@ -14431,7 +14431,7 @@
         <v>38.11962</v>
       </c>
       <c r="H283">
-        <v>457.00215</v>
+        <v>457.0021545</v>
       </c>
     </row>
     <row r="284" spans="1:8">
@@ -14457,7 +14457,7 @@
         <v>24.3961</v>
       </c>
       <c r="H284">
-        <v>208.31083</v>
+        <v>208.3108304</v>
       </c>
     </row>
     <row r="285" spans="1:8">
@@ -14483,7 +14483,7 @@
         <v>52.37431</v>
       </c>
       <c r="H285">
-        <v>259.94329</v>
+        <v>259.9432859</v>
       </c>
     </row>
     <row r="286" spans="1:8">
@@ -14509,7 +14509,7 @@
         <v>34.46181</v>
       </c>
       <c r="H286">
-        <v>241.17468</v>
+        <v>241.1746759</v>
       </c>
     </row>
     <row r="287" spans="1:8">
@@ -14535,7 +14535,7 @@
         <v>72.8352</v>
       </c>
       <c r="H287">
-        <v>226.96329</v>
+        <v>313.8073169</v>
       </c>
     </row>
     <row r="288" spans="1:8">
@@ -14561,7 +14561,7 @@
         <v>113.14933</v>
       </c>
       <c r="H288">
-        <v>332.01169</v>
+        <v>279.6700667</v>
       </c>
     </row>
     <row r="289" spans="1:8">
@@ -14587,7 +14587,7 @@
         <v>271.65904</v>
       </c>
       <c r="H289">
-        <v>556.29187</v>
+        <v>556.2918726</v>
       </c>
     </row>
     <row r="290" spans="1:8">
@@ -14613,7 +14613,7 @@
         <v>259.50467</v>
       </c>
       <c r="H290">
-        <v>544.15678</v>
+        <v>457.3794482</v>
       </c>
     </row>
     <row r="291" spans="1:8">
@@ -14639,7 +14639,7 @@
         <v>93.42277</v>
       </c>
       <c r="H291">
-        <v>263.21842</v>
+        <v>263.2184195</v>
       </c>
     </row>
     <row r="292" spans="1:8">
@@ -14665,7 +14665,7 @@
         <v>88.31731000000001</v>
       </c>
       <c r="H292">
-        <v>261.40551</v>
+        <v>261.4055063</v>
       </c>
     </row>
     <row r="293" spans="1:8">
@@ -14691,7 +14691,7 @@
         <v>95.34169</v>
       </c>
       <c r="H293">
-        <v>261.28094</v>
+        <v>261.2809407</v>
       </c>
     </row>
     <row r="294" spans="1:8">
@@ -14717,7 +14717,7 @@
         <v>88.84224</v>
       </c>
       <c r="H294">
-        <v>257.74363</v>
+        <v>257.7436341</v>
       </c>
     </row>
     <row r="295" spans="1:8">
@@ -14743,7 +14743,7 @@
         <v>85.59616</v>
       </c>
       <c r="H295">
-        <v>259.05015</v>
+        <v>259.0501509</v>
       </c>
     </row>
     <row r="296" spans="1:8">
@@ -14769,7 +14769,7 @@
         <v>92.72778</v>
       </c>
       <c r="H296">
-        <v>258.23898</v>
+        <v>258.2389831</v>
       </c>
     </row>
     <row r="297" spans="1:8">
@@ -14795,7 +14795,7 @@
         <v>89.49793</v>
       </c>
       <c r="H297">
-        <v>263.34372</v>
+        <v>263.3437189</v>
       </c>
     </row>
     <row r="298" spans="1:8">
@@ -14821,7 +14821,7 @@
         <v>93.88132</v>
       </c>
       <c r="H298">
-        <v>259.73138</v>
+        <v>259.7313817</v>
       </c>
     </row>
     <row r="299" spans="1:8">
@@ -14847,7 +14847,7 @@
         <v>120.57148</v>
       </c>
       <c r="H299">
-        <v>436.57929</v>
+        <v>436.5792919</v>
       </c>
     </row>
     <row r="300" spans="1:8">
@@ -14873,7 +14873,7 @@
         <v>213.45027</v>
       </c>
       <c r="H300">
-        <v>539.4460800000001</v>
+        <v>539.4460778</v>
       </c>
     </row>
     <row r="301" spans="1:8">
@@ -14899,7 +14899,7 @@
         <v>100.37368</v>
       </c>
       <c r="H301">
-        <v>337.98392</v>
+        <v>337.9839203</v>
       </c>
     </row>
     <row r="302" spans="1:8">
@@ -14925,7 +14925,7 @@
         <v>47.4431</v>
       </c>
       <c r="H302">
-        <v>349.40535</v>
+        <v>380.9421051</v>
       </c>
     </row>
     <row r="303" spans="1:8">
@@ -14951,7 +14951,7 @@
         <v>70.85355</v>
       </c>
       <c r="H303">
-        <v>239.2368</v>
+        <v>239.2367961</v>
       </c>
     </row>
     <row r="304" spans="1:8">
@@ -14977,7 +14977,7 @@
         <v>74.36448</v>
       </c>
       <c r="H304">
-        <v>240.44039</v>
+        <v>240.4403881</v>
       </c>
     </row>
     <row r="305" spans="1:8">
@@ -15003,7 +15003,7 @@
         <v>113.99658</v>
       </c>
       <c r="H305">
-        <v>333.64135</v>
+        <v>333.6413519</v>
       </c>
     </row>
     <row r="306" spans="1:8">
@@ -15029,7 +15029,7 @@
         <v>81.00684</v>
       </c>
       <c r="H306">
-        <v>248.6566</v>
+        <v>248.6566036</v>
       </c>
     </row>
     <row r="307" spans="1:8">
@@ -15055,7 +15055,7 @@
         <v>73.23381999999999</v>
       </c>
       <c r="H307">
-        <v>241.5677</v>
+        <v>241.5677028</v>
       </c>
     </row>
     <row r="308" spans="1:8">
@@ -15081,7 +15081,7 @@
         <v>86.73304</v>
       </c>
       <c r="H308">
-        <v>252.7373</v>
+        <v>252.7373037</v>
       </c>
     </row>
     <row r="309" spans="1:8">
@@ -15107,7 +15107,7 @@
         <v>86.29458</v>
       </c>
       <c r="H309">
-        <v>254.65714</v>
+        <v>254.6571355</v>
       </c>
     </row>
     <row r="310" spans="1:8">
@@ -15133,7 +15133,7 @@
         <v>80.91719999999999</v>
       </c>
       <c r="H310">
-        <v>251.88722</v>
+        <v>251.8872231</v>
       </c>
     </row>
     <row r="311" spans="1:8">
@@ -15159,7 +15159,7 @@
         <v>88.59989</v>
       </c>
       <c r="H311">
-        <v>253.11311</v>
+        <v>253.1131103</v>
       </c>
     </row>
     <row r="312" spans="1:8">
@@ -15185,7 +15185,7 @@
         <v>159.16032</v>
       </c>
       <c r="H312">
-        <v>466.6516</v>
+        <v>466.6516012</v>
       </c>
     </row>
     <row r="313" spans="1:8">
@@ -15211,7 +15211,7 @@
         <v>95.43939</v>
       </c>
       <c r="H313">
-        <v>265.91947</v>
+        <v>265.9194651</v>
       </c>
     </row>
     <row r="314" spans="1:8">
@@ -15237,7 +15237,7 @@
         <v>94.2213</v>
       </c>
       <c r="H314">
-        <v>258.57106</v>
+        <v>346.2472017</v>
       </c>
     </row>
     <row r="315" spans="1:8">
@@ -15263,7 +15263,7 @@
         <v>88.3507</v>
       </c>
       <c r="H315">
-        <v>271.43115</v>
+        <v>271.4311523</v>
       </c>
     </row>
     <row r="316" spans="1:8">
@@ -15289,7 +15289,7 @@
         <v>66.09478</v>
       </c>
       <c r="H316">
-        <v>218.77916</v>
+        <v>218.7791606</v>
       </c>
     </row>
     <row r="317" spans="1:8">
@@ -15315,7 +15315,7 @@
         <v>78.54186</v>
       </c>
       <c r="H317">
-        <v>246.6728</v>
+        <v>246.6728005</v>
       </c>
     </row>
     <row r="318" spans="1:8">
@@ -15341,7 +15341,7 @@
         <v>28.65542</v>
       </c>
       <c r="H318">
-        <v>146.72306</v>
+        <v>146.7230633</v>
       </c>
     </row>
     <row r="319" spans="1:8">
@@ -15367,7 +15367,7 @@
         <v>44.55194</v>
       </c>
       <c r="H319">
-        <v>193.88559</v>
+        <v>279.8437618</v>
       </c>
     </row>
     <row r="320" spans="1:8">
@@ -15393,7 +15393,7 @@
         <v>27.22474</v>
       </c>
       <c r="H320">
-        <v>136.40786</v>
+        <v>136.4078587</v>
       </c>
     </row>
     <row r="321" spans="1:8">
@@ -15419,7 +15419,7 @@
         <v>168.46511</v>
       </c>
       <c r="H321">
-        <v>393.01157</v>
+        <v>393.0115732</v>
       </c>
     </row>
     <row r="322" spans="1:8">
@@ -15445,7 +15445,7 @@
         <v>80.31856000000001</v>
       </c>
       <c r="H322">
-        <v>240.67065</v>
+        <v>294.9219869</v>
       </c>
     </row>
     <row r="323" spans="1:8">
@@ -15471,7 +15471,7 @@
         <v>81.82874</v>
       </c>
       <c r="H323">
-        <v>280.03487</v>
+        <v>280.034874</v>
       </c>
     </row>
     <row r="324" spans="1:8">
@@ -15497,7 +15497,7 @@
         <v>79.21719</v>
       </c>
       <c r="H324">
-        <v>268.65736</v>
+        <v>268.6573565</v>
       </c>
     </row>
     <row r="325" spans="1:8">
@@ -15523,7 +15523,7 @@
         <v>87.17440000000001</v>
       </c>
       <c r="H325">
-        <v>309.87928</v>
+        <v>292.5440546</v>
       </c>
     </row>
     <row r="326" spans="1:8">
@@ -15549,7 +15549,7 @@
         <v>104.04794</v>
       </c>
       <c r="H326">
-        <v>332.66353</v>
+        <v>329.7817864</v>
       </c>
     </row>
     <row r="327" spans="1:8">
@@ -15575,7 +15575,7 @@
         <v>24.54869</v>
       </c>
       <c r="H327">
-        <v>419.90849</v>
+        <v>419.908489</v>
       </c>
     </row>
     <row r="328" spans="1:8">
@@ -15601,7 +15601,7 @@
         <v>110.13804</v>
       </c>
       <c r="H328">
-        <v>495.75806</v>
+        <v>549.4936704</v>
       </c>
     </row>
     <row r="329" spans="1:8">
@@ -15627,7 +15627,7 @@
         <v>37.68118</v>
       </c>
       <c r="H329">
-        <v>191.91248</v>
+        <v>191.912482</v>
       </c>
     </row>
     <row r="330" spans="1:8">
@@ -15653,7 +15653,7 @@
         <v>88.58508999999999</v>
       </c>
       <c r="H330">
-        <v>304.29666</v>
+        <v>304.2966643</v>
       </c>
     </row>
     <row r="331" spans="1:8">
@@ -15679,7 +15679,7 @@
         <v>61.75977</v>
       </c>
       <c r="H331">
-        <v>222.57011</v>
+        <v>222.5701058</v>
       </c>
     </row>
     <row r="332" spans="1:8">
@@ -15705,7 +15705,7 @@
         <v>25.7789</v>
       </c>
       <c r="H332">
-        <v>132.15873</v>
+        <v>132.158727</v>
       </c>
     </row>
     <row r="333" spans="1:8">
@@ -15731,7 +15731,7 @@
         <v>86.41895</v>
       </c>
       <c r="H333">
-        <v>304.22031</v>
+        <v>304.2203056</v>
       </c>
     </row>
     <row r="334" spans="1:8">
@@ -15757,7 +15757,7 @@
         <v>47.27208</v>
       </c>
       <c r="H334">
-        <v>194.4927</v>
+        <v>194.4926999</v>
       </c>
     </row>
     <row r="335" spans="1:8">
@@ -15783,7 +15783,7 @@
         <v>36.87664</v>
       </c>
       <c r="H335">
-        <v>185.59155</v>
+        <v>185.591547</v>
       </c>
     </row>
     <row r="336" spans="1:8">
@@ -15809,7 +15809,7 @@
         <v>88.95524</v>
       </c>
       <c r="H336">
-        <v>298.38588</v>
+        <v>329.3200404</v>
       </c>
     </row>
     <row r="337" spans="1:8">
@@ -15835,7 +15835,7 @@
         <v>165.21445</v>
       </c>
       <c r="H337">
-        <v>344.65131</v>
+        <v>397.4233018</v>
       </c>
     </row>
     <row r="338" spans="1:8">
@@ -15861,7 +15861,7 @@
         <v>126.14537</v>
       </c>
       <c r="H338">
-        <v>273.66638</v>
+        <v>273.6663834</v>
       </c>
     </row>
     <row r="339" spans="1:8">
@@ -15887,7 +15887,7 @@
         <v>29.91946</v>
       </c>
       <c r="H339">
-        <v>175.21243</v>
+        <v>175.2124272</v>
       </c>
     </row>
     <row r="340" spans="1:8">
@@ -15913,7 +15913,7 @@
         <v>87.36453</v>
       </c>
       <c r="H340">
-        <v>308.02402</v>
+        <v>330.5009903</v>
       </c>
     </row>
     <row r="341" spans="1:8">
@@ -15939,7 +15939,7 @@
         <v>75.85885</v>
       </c>
       <c r="H341">
-        <v>209.05808</v>
+        <v>209.0580834</v>
       </c>
     </row>
     <row r="342" spans="1:8">
@@ -15965,7 +15965,7 @@
         <v>51.49788</v>
       </c>
       <c r="H342">
-        <v>233.9035</v>
+        <v>323.121824</v>
       </c>
     </row>
     <row r="343" spans="1:8">
@@ -15991,7 +15991,7 @@
         <v>139.92742</v>
       </c>
       <c r="H343">
-        <v>314.42156</v>
+        <v>314.4215647</v>
       </c>
     </row>
     <row r="344" spans="1:8">
@@ -16017,7 +16017,7 @@
         <v>44.61511</v>
       </c>
       <c r="H344">
-        <v>183.17305</v>
+        <v>183.1730516</v>
       </c>
     </row>
     <row r="345" spans="1:8">
@@ -16043,7 +16043,7 @@
         <v>69.88856</v>
       </c>
       <c r="H345">
-        <v>239.75202</v>
+        <v>239.7520179</v>
       </c>
     </row>
     <row r="346" spans="1:8">
@@ -16069,7 +16069,7 @@
         <v>33.41995</v>
       </c>
       <c r="H346">
-        <v>179.05482</v>
+        <v>179.0548193</v>
       </c>
     </row>
     <row r="347" spans="1:8">
@@ -16095,7 +16095,7 @@
         <v>67.12291</v>
       </c>
       <c r="H347">
-        <v>302.21757</v>
+        <v>302.2175661</v>
       </c>
     </row>
     <row r="348" spans="1:8">
@@ -16121,7 +16121,7 @@
         <v>96.47403</v>
       </c>
       <c r="H348">
-        <v>301.3548</v>
+        <v>387.8566236</v>
       </c>
     </row>
     <row r="349" spans="1:8">
@@ -16147,7 +16147,7 @@
         <v>53.54448</v>
       </c>
       <c r="H349">
-        <v>268.6746</v>
+        <v>268.6746047</v>
       </c>
     </row>
     <row r="350" spans="1:8">
@@ -16173,7 +16173,7 @@
         <v>25.31584</v>
       </c>
       <c r="H350">
-        <v>213.27118</v>
+        <v>213.271176</v>
       </c>
     </row>
     <row r="351" spans="1:8">
@@ -16199,7 +16199,7 @@
         <v>47.12283</v>
       </c>
       <c r="H351">
-        <v>191.59953</v>
+        <v>191.5995306</v>
       </c>
     </row>
     <row r="352" spans="1:8">
@@ -16225,7 +16225,7 @@
         <v>321.73327</v>
       </c>
       <c r="H352">
-        <v>722.82061</v>
+        <v>722.8206104</v>
       </c>
     </row>
     <row r="353" spans="1:8">
@@ -16251,7 +16251,7 @@
         <v>282.38665</v>
       </c>
       <c r="H353">
-        <v>460.82881</v>
+        <v>460.8288148</v>
       </c>
     </row>
     <row r="354" spans="1:8">
@@ -16277,7 +16277,7 @@
         <v>92.03867</v>
       </c>
       <c r="H354">
-        <v>516.83036</v>
+        <v>516.8303614</v>
       </c>
     </row>
     <row r="355" spans="1:8">
@@ -16303,7 +16303,7 @@
         <v>276.30618</v>
       </c>
       <c r="H355">
-        <v>456.58429</v>
+        <v>456.5842921</v>
       </c>
     </row>
     <row r="356" spans="1:8">
@@ -16329,7 +16329,7 @@
         <v>122.441</v>
       </c>
       <c r="H356">
-        <v>309.09766</v>
+        <v>309.0976597</v>
       </c>
     </row>
     <row r="357" spans="1:8">
@@ -16355,7 +16355,7 @@
         <v>264.87706</v>
       </c>
       <c r="H357">
-        <v>576.01833</v>
+        <v>576.0183346</v>
       </c>
     </row>
     <row r="358" spans="1:8">
@@ -16381,7 +16381,7 @@
         <v>256.35592</v>
       </c>
       <c r="H358">
-        <v>567.54095</v>
+        <v>567.5409491</v>
       </c>
     </row>
     <row r="359" spans="1:8">
@@ -16407,7 +16407,7 @@
         <v>224.22991</v>
       </c>
       <c r="H359">
-        <v>518.09582</v>
+        <v>486.2098143</v>
       </c>
     </row>
     <row r="360" spans="1:8">
@@ -16433,7 +16433,7 @@
         <v>131.83272</v>
       </c>
       <c r="H360">
-        <v>406.10709</v>
+        <v>422.0910755</v>
       </c>
     </row>
     <row r="361" spans="1:8">
@@ -16459,7 +16459,7 @@
         <v>41.81299</v>
       </c>
       <c r="H361">
-        <v>250.49695</v>
+        <v>250.4969531</v>
       </c>
     </row>
     <row r="362" spans="1:8">
@@ -16485,7 +16485,7 @@
         <v>99.0264</v>
       </c>
       <c r="H362">
-        <v>403.77989</v>
+        <v>403.7798893</v>
       </c>
     </row>
     <row r="363" spans="1:8">
@@ -16511,7 +16511,7 @@
         <v>72.05094</v>
       </c>
       <c r="H363">
-        <v>260.46131</v>
+        <v>243.4326784</v>
       </c>
     </row>
     <row r="364" spans="1:8">
@@ -16537,7 +16537,7 @@
         <v>106.45773</v>
       </c>
       <c r="H364">
-        <v>485.3105</v>
+        <v>485.3105002</v>
       </c>
     </row>
     <row r="365" spans="1:8">
@@ -16563,7 +16563,7 @@
         <v>80.75172000000001</v>
       </c>
       <c r="H365">
-        <v>326.20288</v>
+        <v>326.2028839</v>
       </c>
     </row>
     <row r="366" spans="1:8">
@@ -16589,7 +16589,7 @@
         <v>60.65578</v>
       </c>
       <c r="H366">
-        <v>217.40127</v>
+        <v>217.4012692</v>
       </c>
     </row>
     <row r="367" spans="1:8">
@@ -16615,7 +16615,7 @@
         <v>71.57689000000001</v>
       </c>
       <c r="H367">
-        <v>212.69301</v>
+        <v>212.6930081</v>
       </c>
     </row>
     <row r="368" spans="1:8">
@@ -16641,7 +16641,7 @@
         <v>57.724</v>
       </c>
       <c r="H368">
-        <v>272.84597</v>
+        <v>272.8459697</v>
       </c>
     </row>
     <row r="369" spans="1:8">
@@ -16667,7 +16667,7 @@
         <v>151.38155</v>
       </c>
       <c r="H369">
-        <v>370.80337</v>
+        <v>439.4074579</v>
       </c>
     </row>
     <row r="370" spans="1:8">
@@ -16693,7 +16693,7 @@
         <v>111.42598</v>
       </c>
       <c r="H370">
-        <v>312.44993</v>
+        <v>312.449925</v>
       </c>
     </row>
     <row r="371" spans="1:8">
@@ -16719,7 +16719,7 @@
         <v>131.49072</v>
       </c>
       <c r="H371">
-        <v>367.052</v>
+        <v>367.0519965</v>
       </c>
     </row>
     <row r="372" spans="1:8">
@@ -16745,7 +16745,7 @@
         <v>143.79553</v>
       </c>
       <c r="H372">
-        <v>397.61907</v>
+        <v>397.6190722</v>
       </c>
     </row>
     <row r="373" spans="1:8">
@@ -16771,7 +16771,7 @@
         <v>180.94264</v>
       </c>
       <c r="H373">
-        <v>404.21156</v>
+        <v>404.2115642</v>
       </c>
     </row>
     <row r="374" spans="1:8">
@@ -16797,7 +16797,7 @@
         <v>94.77336</v>
       </c>
       <c r="H374">
-        <v>306.7214</v>
+        <v>306.7214013</v>
       </c>
     </row>
     <row r="375" spans="1:8">
@@ -16823,7 +16823,7 @@
         <v>170.30057</v>
       </c>
       <c r="H375">
-        <v>439.62013</v>
+        <v>439.6201307</v>
       </c>
     </row>
     <row r="376" spans="1:8">
@@ -16849,7 +16849,7 @@
         <v>54.99208</v>
       </c>
       <c r="H376">
-        <v>213.36541</v>
+        <v>213.3654056</v>
       </c>
     </row>
     <row r="377" spans="1:8">
@@ -16875,7 +16875,7 @@
         <v>22.50219</v>
       </c>
       <c r="H377">
-        <v>133.7085</v>
+        <v>133.7084996</v>
       </c>
     </row>
     <row r="378" spans="1:8">
@@ -16901,7 +16901,7 @@
         <v>53.4812</v>
       </c>
       <c r="H378">
-        <v>219.91377</v>
+        <v>219.9137679</v>
       </c>
     </row>
     <row r="379" spans="1:8">
@@ -16927,7 +16927,7 @@
         <v>48.67362</v>
       </c>
       <c r="H379">
-        <v>206.12025</v>
+        <v>206.120247</v>
       </c>
     </row>
     <row r="380" spans="1:8">
@@ -16953,7 +16953,7 @@
         <v>56.15148</v>
       </c>
       <c r="H380">
-        <v>225.83261</v>
+        <v>225.8326061</v>
       </c>
     </row>
     <row r="381" spans="1:8">
@@ -16979,7 +16979,7 @@
         <v>22.3872</v>
       </c>
       <c r="H381">
-        <v>142.29656</v>
+        <v>142.2965563</v>
       </c>
     </row>
     <row r="382" spans="1:8">
@@ -17005,7 +17005,7 @@
         <v>23.2309</v>
       </c>
       <c r="H382">
-        <v>124.81095</v>
+        <v>124.8109531</v>
       </c>
     </row>
     <row r="383" spans="1:8">
@@ -17031,7 +17031,7 @@
         <v>182.71896</v>
       </c>
       <c r="H383">
-        <v>437.0064</v>
+        <v>437.0064029</v>
       </c>
     </row>
     <row r="384" spans="1:8">
@@ -17057,7 +17057,7 @@
         <v>91.71249</v>
       </c>
       <c r="H384">
-        <v>260.02531</v>
+        <v>260.0253132</v>
       </c>
     </row>
     <row r="385" spans="1:8">
@@ -17083,7 +17083,7 @@
         <v>73.33924</v>
       </c>
       <c r="H385">
-        <v>300.40571</v>
+        <v>300.4057135</v>
       </c>
     </row>
     <row r="386" spans="1:8">
@@ -17109,7 +17109,7 @@
         <v>75.79782</v>
       </c>
       <c r="H386">
-        <v>307.59986</v>
+        <v>307.5998636</v>
       </c>
     </row>
     <row r="387" spans="1:8">
@@ -17135,7 +17135,7 @@
         <v>151.43253</v>
       </c>
       <c r="H387">
-        <v>404.84547</v>
+        <v>404.8454678</v>
       </c>
     </row>
     <row r="388" spans="1:8">
@@ -17161,7 +17161,7 @@
         <v>22.08917</v>
       </c>
       <c r="H388">
-        <v>197.13613</v>
+        <v>197.1361272</v>
       </c>
     </row>
     <row r="389" spans="1:8">
@@ -17187,7 +17187,7 @@
         <v>18.21873</v>
       </c>
       <c r="H389">
-        <v>160.38814</v>
+        <v>160.3881431</v>
       </c>
     </row>
     <row r="390" spans="1:8">
@@ -17213,7 +17213,7 @@
         <v>38.53297</v>
       </c>
       <c r="H390">
-        <v>260.91479</v>
+        <v>260.9147865</v>
       </c>
     </row>
     <row r="391" spans="1:8">
@@ -17239,7 +17239,7 @@
         <v>158.16102</v>
       </c>
       <c r="H391">
-        <v>480.826</v>
+        <v>480.8260018</v>
       </c>
     </row>
     <row r="392" spans="1:8">
@@ -17265,7 +17265,7 @@
         <v>84.60590000000001</v>
       </c>
       <c r="H392">
-        <v>413.99654</v>
+        <v>413.9965372</v>
       </c>
     </row>
     <row r="393" spans="1:8">
@@ -17291,7 +17291,7 @@
         <v>59.30704</v>
       </c>
       <c r="H393">
-        <v>265.1802</v>
+        <v>265.180202</v>
       </c>
     </row>
     <row r="394" spans="1:8">
@@ -17317,7 +17317,7 @@
         <v>70.15158</v>
       </c>
       <c r="H394">
-        <v>327.7937</v>
+        <v>327.7936986</v>
       </c>
     </row>
     <row r="395" spans="1:8">
@@ -17343,7 +17343,7 @@
         <v>29.95786</v>
       </c>
       <c r="H395">
-        <v>211.85443</v>
+        <v>241.1904871</v>
       </c>
     </row>
     <row r="396" spans="1:8">
@@ -17369,7 +17369,7 @@
         <v>58.49774</v>
       </c>
       <c r="H396">
-        <v>331.52359</v>
+        <v>368.492358</v>
       </c>
     </row>
     <row r="397" spans="1:8">
@@ -17395,7 +17395,7 @@
         <v>89.18934</v>
       </c>
       <c r="H397">
-        <v>266.91607</v>
+        <v>266.9160703</v>
       </c>
     </row>
     <row r="398" spans="1:8">
@@ -17421,7 +17421,7 @@
         <v>143.61743</v>
       </c>
       <c r="H398">
-        <v>437.68519</v>
+        <v>437.6851945</v>
       </c>
     </row>
     <row r="399" spans="1:8">
@@ -17447,7 +17447,7 @@
         <v>152.58333</v>
       </c>
       <c r="H399">
-        <v>341.9876</v>
+        <v>341.987605</v>
       </c>
     </row>
     <row r="400" spans="1:8">
@@ -17473,7 +17473,7 @@
         <v>152.03773</v>
       </c>
       <c r="H400">
-        <v>400.88751</v>
+        <v>400.8875051</v>
       </c>
     </row>
     <row r="401" spans="1:8">
@@ -17499,7 +17499,7 @@
         <v>87.92834999999999</v>
       </c>
       <c r="H401">
-        <v>268.02804</v>
+        <v>268.0280422</v>
       </c>
     </row>
     <row r="402" spans="1:8">
@@ -17525,7 +17525,7 @@
         <v>30.39978</v>
       </c>
       <c r="H402">
-        <v>169.44553</v>
+        <v>169.4455346</v>
       </c>
     </row>
     <row r="403" spans="1:8">
@@ -17551,7 +17551,7 @@
         <v>13.36928</v>
       </c>
       <c r="H403">
-        <v>116.4549</v>
+        <v>116.4549025</v>
       </c>
     </row>
     <row r="404" spans="1:8">
@@ -17577,7 +17577,7 @@
         <v>11.73772</v>
       </c>
       <c r="H404">
-        <v>109.69876</v>
+        <v>109.6987565</v>
       </c>
     </row>
     <row r="405" spans="1:8">
@@ -17603,7 +17603,7 @@
         <v>31.6743</v>
       </c>
       <c r="H405">
-        <v>203.94761</v>
+        <v>203.9476084</v>
       </c>
     </row>
     <row r="406" spans="1:8">
@@ -17629,7 +17629,7 @@
         <v>20.80506</v>
       </c>
       <c r="H406">
-        <v>191.451</v>
+        <v>191.4509959</v>
       </c>
     </row>
     <row r="407" spans="1:8">
@@ -17655,7 +17655,7 @@
         <v>94.95432</v>
       </c>
       <c r="H407">
-        <v>270.09904</v>
+        <v>270.0990395</v>
       </c>
     </row>
     <row r="408" spans="1:8">
@@ -17681,7 +17681,7 @@
         <v>152.26654</v>
       </c>
       <c r="H408">
-        <v>444.52595</v>
+        <v>444.5259478</v>
       </c>
     </row>
     <row r="409" spans="1:8">
@@ -17707,7 +17707,7 @@
         <v>100.01372</v>
       </c>
       <c r="H409">
-        <v>269.59226</v>
+        <v>269.5922579</v>
       </c>
     </row>
     <row r="410" spans="1:8">
@@ -17733,7 +17733,7 @@
         <v>160.26421</v>
       </c>
       <c r="H410">
-        <v>447.18206</v>
+        <v>447.1820567</v>
       </c>
     </row>
     <row r="411" spans="1:8">
@@ -17759,7 +17759,7 @@
         <v>36.16923</v>
       </c>
       <c r="H411">
-        <v>210.00687</v>
+        <v>210.0068737</v>
       </c>
     </row>
     <row r="412" spans="1:8">
@@ -17785,7 +17785,7 @@
         <v>72.89731999999999</v>
       </c>
       <c r="H412">
-        <v>323.45509</v>
+        <v>323.4550913</v>
       </c>
     </row>
     <row r="413" spans="1:8">
@@ -17811,7 +17811,7 @@
         <v>24.75943</v>
       </c>
       <c r="H413">
-        <v>160.70619</v>
+        <v>160.7061886</v>
       </c>
     </row>
     <row r="414" spans="1:8">
@@ -17837,7 +17837,7 @@
         <v>143.9077</v>
       </c>
       <c r="H414">
-        <v>453.79268</v>
+        <v>453.7926774</v>
       </c>
     </row>
     <row r="415" spans="1:8">
@@ -17863,7 +17863,7 @@
         <v>189.54652</v>
       </c>
       <c r="H415">
-        <v>540.98925</v>
+        <v>540.9892538</v>
       </c>
     </row>
     <row r="416" spans="1:8">
@@ -17889,7 +17889,7 @@
         <v>208.39909</v>
       </c>
       <c r="H416">
-        <v>575.12978</v>
+        <v>575.129777</v>
       </c>
     </row>
     <row r="417" spans="1:8">
@@ -17915,7 +17915,7 @@
         <v>78.34424</v>
       </c>
       <c r="H417">
-        <v>293.84175</v>
+        <v>293.8417541</v>
       </c>
     </row>
     <row r="418" spans="1:8">
@@ -17941,7 +17941,7 @@
         <v>82.34641999999999</v>
       </c>
       <c r="H418">
-        <v>327.65263</v>
+        <v>327.6526264</v>
       </c>
     </row>
     <row r="419" spans="1:8">
@@ -17967,7 +17967,7 @@
         <v>68.23309999999999</v>
       </c>
       <c r="H419">
-        <v>256.56167</v>
+        <v>256.5616716</v>
       </c>
     </row>
     <row r="420" spans="1:8">
@@ -17993,7 +17993,7 @@
         <v>109.85385</v>
       </c>
       <c r="H420">
-        <v>421.26763</v>
+        <v>421.2676267</v>
       </c>
     </row>
     <row r="421" spans="1:8">
@@ -18019,7 +18019,7 @@
         <v>83.97744</v>
       </c>
       <c r="H421">
-        <v>269.5779</v>
+        <v>269.5779042</v>
       </c>
     </row>
     <row r="422" spans="1:8">
@@ -18045,7 +18045,7 @@
         <v>31.07941</v>
       </c>
       <c r="H422">
-        <v>142.44469</v>
+        <v>142.4446852</v>
       </c>
     </row>
     <row r="423" spans="1:8">
@@ -18071,7 +18071,7 @@
         <v>91.15558</v>
       </c>
       <c r="H423">
-        <v>330.149</v>
+        <v>330.1489966</v>
       </c>
     </row>
     <row r="424" spans="1:8">
@@ -18097,7 +18097,7 @@
         <v>225.15078</v>
       </c>
       <c r="H424">
-        <v>516.87816</v>
+        <v>516.8781613</v>
       </c>
     </row>
     <row r="425" spans="1:8">
@@ -18123,7 +18123,7 @@
         <v>252.785</v>
       </c>
       <c r="H425">
-        <v>646.30336</v>
+        <v>646.3033607</v>
       </c>
     </row>
     <row r="426" spans="1:8">
@@ -18149,7 +18149,7 @@
         <v>124.67539</v>
       </c>
       <c r="H426">
-        <v>372.58176</v>
+        <v>372.5817647</v>
       </c>
     </row>
     <row r="427" spans="1:8">
@@ -18175,7 +18175,7 @@
         <v>57.03358</v>
       </c>
       <c r="H427">
-        <v>250.20375</v>
+        <v>250.2037474</v>
       </c>
     </row>
     <row r="428" spans="1:8">
@@ -18201,7 +18201,7 @@
         <v>161.66304</v>
       </c>
       <c r="H428">
-        <v>472.05943</v>
+        <v>472.0594259</v>
       </c>
     </row>
     <row r="429" spans="1:8">
@@ -18227,7 +18227,7 @@
         <v>172.49382</v>
       </c>
       <c r="H429">
-        <v>481.04302</v>
+        <v>481.0430219</v>
       </c>
     </row>
     <row r="430" spans="1:8">
@@ -18253,7 +18253,7 @@
         <v>143.50302</v>
       </c>
       <c r="H430">
-        <v>416.22863</v>
+        <v>416.2286298</v>
       </c>
     </row>
     <row r="431" spans="1:8">
@@ -18279,7 +18279,7 @@
         <v>166.2882</v>
       </c>
       <c r="H431">
-        <v>475.0563</v>
+        <v>475.0563022</v>
       </c>
     </row>
     <row r="432" spans="1:8">
@@ -18305,7 +18305,7 @@
         <v>174.09831</v>
       </c>
       <c r="H432">
-        <v>443.26376</v>
+        <v>443.2637555</v>
       </c>
     </row>
     <row r="433" spans="1:8">
@@ -18331,7 +18331,7 @@
         <v>198.51262</v>
       </c>
       <c r="H433">
-        <v>743.88611</v>
+        <v>743.8861063000001</v>
       </c>
     </row>
     <row r="434" spans="1:8">
@@ -18383,7 +18383,7 @@
         <v>163.865</v>
       </c>
       <c r="H435">
-        <v>433.50341</v>
+        <v>521.2097102</v>
       </c>
     </row>
     <row r="436" spans="1:8">
@@ -18409,7 +18409,7 @@
         <v>98.621</v>
       </c>
       <c r="H436">
-        <v>364.7845</v>
+        <v>364.7844973</v>
       </c>
     </row>
     <row r="437" spans="1:8">
@@ -18435,7 +18435,7 @@
         <v>108.40723</v>
       </c>
       <c r="H437">
-        <v>380.07687</v>
+        <v>378.2740199</v>
       </c>
     </row>
     <row r="438" spans="1:8">
@@ -18461,7 +18461,7 @@
         <v>123.75405</v>
       </c>
       <c r="H438">
-        <v>393.07531</v>
+        <v>393.0753065</v>
       </c>
     </row>
     <row r="439" spans="1:8">
@@ -18487,7 +18487,7 @@
         <v>175.22904</v>
       </c>
       <c r="H439">
-        <v>579.7536700000001</v>
+        <v>579.7536708</v>
       </c>
     </row>
     <row r="440" spans="1:8">
@@ -18513,7 +18513,7 @@
         <v>199.76418</v>
       </c>
       <c r="H440">
-        <v>700.29707</v>
+        <v>700.2970673999999</v>
       </c>
     </row>
     <row r="441" spans="1:8">
@@ -18539,7 +18539,7 @@
         <v>69.98779999999999</v>
       </c>
       <c r="H441">
-        <v>297.73608</v>
+        <v>365.8224986</v>
       </c>
     </row>
     <row r="442" spans="1:8">
@@ -18565,7 +18565,7 @@
         <v>155.79912</v>
       </c>
       <c r="H442">
-        <v>416.35272</v>
+        <v>416.3527232</v>
       </c>
     </row>
     <row r="443" spans="1:8">
@@ -18591,7 +18591,7 @@
         <v>130.8754</v>
       </c>
       <c r="H443">
-        <v>524.38144</v>
+        <v>524.3814419</v>
       </c>
     </row>
     <row r="444" spans="1:8">
@@ -18617,7 +18617,7 @@
         <v>156.94944</v>
       </c>
       <c r="H444">
-        <v>549.85522</v>
+        <v>637.6445903</v>
       </c>
     </row>
     <row r="445" spans="1:8">
@@ -18643,7 +18643,7 @@
         <v>86.24575</v>
       </c>
       <c r="H445">
-        <v>372.33533</v>
+        <v>423.264838</v>
       </c>
     </row>
     <row r="446" spans="1:8">
@@ -18669,7 +18669,7 @@
         <v>250.8601</v>
       </c>
       <c r="H446">
-        <v>688.38939</v>
+        <v>643.9694111</v>
       </c>
     </row>
     <row r="447" spans="1:8">
@@ -18695,7 +18695,7 @@
         <v>126.17269</v>
       </c>
       <c r="H447">
-        <v>353.36238</v>
+        <v>353.3623841</v>
       </c>
     </row>
     <row r="448" spans="1:8">
@@ -18721,7 +18721,7 @@
         <v>77.77764000000001</v>
       </c>
       <c r="H448">
-        <v>253.96354</v>
+        <v>253.9635426</v>
       </c>
     </row>
     <row r="449" spans="1:8">
@@ -18747,7 +18747,7 @@
         <v>62.92213</v>
       </c>
       <c r="H449">
-        <v>349.26045</v>
+        <v>349.2604487</v>
       </c>
     </row>
     <row r="450" spans="1:8">
@@ -18773,7 +18773,7 @@
         <v>35.89784</v>
       </c>
       <c r="H450">
-        <v>249.32712</v>
+        <v>249.3271246</v>
       </c>
     </row>
     <row r="451" spans="1:8">
@@ -18799,7 +18799,7 @@
         <v>158.72942</v>
       </c>
       <c r="H451">
-        <v>606.28844</v>
+        <v>530.1495617</v>
       </c>
     </row>
     <row r="452" spans="1:8">
@@ -18825,7 +18825,7 @@
         <v>31.65043</v>
       </c>
       <c r="H452">
-        <v>203.08513</v>
+        <v>203.0851259</v>
       </c>
     </row>
     <row r="453" spans="1:8">
@@ -18851,7 +18851,7 @@
         <v>122.42006</v>
       </c>
       <c r="H453">
-        <v>350.4946</v>
+        <v>419.192707</v>
       </c>
     </row>
     <row r="454" spans="1:8">
@@ -18877,7 +18877,7 @@
         <v>193.6246</v>
       </c>
       <c r="H454">
-        <v>672.6326299999999</v>
+        <v>672.6326265</v>
       </c>
     </row>
     <row r="455" spans="1:8">
@@ -18903,7 +18903,7 @@
         <v>62.22216</v>
       </c>
       <c r="H455">
-        <v>264.08954</v>
+        <v>264.0895394</v>
       </c>
     </row>
     <row r="456" spans="1:8">
@@ -18929,7 +18929,7 @@
         <v>116.56487</v>
       </c>
       <c r="H456">
-        <v>399.84725</v>
+        <v>399.8472477</v>
       </c>
     </row>
     <row r="457" spans="1:8">
@@ -18955,7 +18955,7 @@
         <v>158.33963</v>
       </c>
       <c r="H457">
-        <v>432.90488</v>
+        <v>432.9048846</v>
       </c>
     </row>
     <row r="458" spans="1:8">
@@ -18981,7 +18981,7 @@
         <v>119.14789</v>
       </c>
       <c r="H458">
-        <v>425.44426</v>
+        <v>425.4442597</v>
       </c>
     </row>
     <row r="459" spans="1:8">
@@ -19007,7 +19007,7 @@
         <v>79.31384</v>
       </c>
       <c r="H459">
-        <v>594.75541</v>
+        <v>594.7554138</v>
       </c>
     </row>
     <row r="460" spans="1:8">
@@ -19033,7 +19033,7 @@
         <v>88.14832</v>
       </c>
       <c r="H460">
-        <v>314.43801</v>
+        <v>314.4380077</v>
       </c>
     </row>
     <row r="461" spans="1:8">
@@ -19059,7 +19059,7 @@
         <v>91.96816</v>
       </c>
       <c r="H461">
-        <v>588.20209</v>
+        <v>588.2020854</v>
       </c>
     </row>
     <row r="462" spans="1:8">
@@ -19085,7 +19085,7 @@
         <v>11.07568</v>
       </c>
       <c r="H462">
-        <v>251.48792</v>
+        <v>251.4879218</v>
       </c>
     </row>
     <row r="463" spans="1:8">
@@ -19111,7 +19111,7 @@
         <v>83.88198</v>
       </c>
       <c r="H463">
-        <v>371.82931</v>
+        <v>371.8293143</v>
       </c>
     </row>
     <row r="464" spans="1:8">
@@ -19137,7 +19137,7 @@
         <v>27.6609</v>
       </c>
       <c r="H464">
-        <v>239.44652</v>
+        <v>239.4465187</v>
       </c>
     </row>
     <row r="465" spans="1:8">
@@ -19163,7 +19163,7 @@
         <v>24.15014</v>
       </c>
       <c r="H465">
-        <v>200.04476</v>
+        <v>200.0447565</v>
       </c>
     </row>
     <row r="466" spans="1:8">
@@ -19189,7 +19189,7 @@
         <v>127.14585</v>
       </c>
       <c r="H466">
-        <v>496.57685</v>
+        <v>496.5768453</v>
       </c>
     </row>
     <row r="467" spans="1:8">
@@ -19215,7 +19215,7 @@
         <v>180.57095</v>
       </c>
       <c r="H467">
-        <v>472.2767</v>
+        <v>472.2766992</v>
       </c>
     </row>
     <row r="468" spans="1:8">
@@ -19241,7 +19241,7 @@
         <v>55.56852</v>
       </c>
       <c r="H468">
-        <v>401.65598</v>
+        <v>401.6559847</v>
       </c>
     </row>
     <row r="469" spans="1:8">
@@ -19267,7 +19267,7 @@
         <v>99.41745</v>
       </c>
       <c r="H469">
-        <v>421.35462</v>
+        <v>421.3546224</v>
       </c>
     </row>
     <row r="470" spans="1:8">
@@ -19293,7 +19293,7 @@
         <v>53.64429</v>
       </c>
       <c r="H470">
-        <v>202.0996</v>
+        <v>275.6713903</v>
       </c>
     </row>
     <row r="471" spans="1:8">
@@ -19319,7 +19319,7 @@
         <v>107.31637</v>
       </c>
       <c r="H471">
-        <v>363.31075</v>
+        <v>363.3107464</v>
       </c>
     </row>
     <row r="472" spans="1:8">
@@ -19345,7 +19345,7 @@
         <v>128.98389</v>
       </c>
       <c r="H472">
-        <v>436.06862</v>
+        <v>481.3248039</v>
       </c>
     </row>
     <row r="473" spans="1:8">
@@ -19371,7 +19371,7 @@
         <v>123.86805</v>
       </c>
       <c r="H473">
-        <v>386.63443</v>
+        <v>386.6344315</v>
       </c>
     </row>
     <row r="474" spans="1:8">
@@ -19397,7 +19397,7 @@
         <v>84.31325</v>
       </c>
       <c r="H474">
-        <v>289.70825</v>
+        <v>289.7082464</v>
       </c>
     </row>
     <row r="475" spans="1:8">
@@ -19423,7 +19423,7 @@
         <v>95.97447</v>
       </c>
       <c r="H475">
-        <v>251.96189</v>
+        <v>251.9618869</v>
       </c>
     </row>
     <row r="476" spans="1:8">
@@ -19449,7 +19449,7 @@
         <v>52.65607</v>
       </c>
       <c r="H476">
-        <v>457.22761</v>
+        <v>457.2276061</v>
       </c>
     </row>
     <row r="477" spans="1:8">
@@ -19475,7 +19475,7 @@
         <v>194.51555</v>
       </c>
       <c r="H477">
-        <v>493.51918</v>
+        <v>474.4592772</v>
       </c>
     </row>
     <row r="478" spans="1:8">
@@ -19501,7 +19501,7 @@
         <v>165.862</v>
       </c>
       <c r="H478">
-        <v>376.26438</v>
+        <v>354.9401096</v>
       </c>
     </row>
     <row r="479" spans="1:8">
@@ -19527,7 +19527,7 @@
         <v>15.70429</v>
       </c>
       <c r="H479">
-        <v>147.92628</v>
+        <v>147.9262778</v>
       </c>
     </row>
     <row r="480" spans="1:8">
@@ -19553,7 +19553,7 @@
         <v>152.93058</v>
       </c>
       <c r="H480">
-        <v>368.69418</v>
+        <v>368.694176</v>
       </c>
     </row>
     <row r="481" spans="1:8">
@@ -19579,7 +19579,7 @@
         <v>105.41086</v>
       </c>
       <c r="H481">
-        <v>321.15583</v>
+        <v>366.5220516</v>
       </c>
     </row>
     <row r="482" spans="1:8">
@@ -19605,7 +19605,7 @@
         <v>96.36144</v>
       </c>
       <c r="H482">
-        <v>676.87085</v>
+        <v>676.8708543</v>
       </c>
     </row>
     <row r="483" spans="1:8">
@@ -19631,7 +19631,7 @@
         <v>28.66732</v>
       </c>
       <c r="H483">
-        <v>205.45218</v>
+        <v>205.4521821</v>
       </c>
     </row>
     <row r="484" spans="1:8">
@@ -19657,7 +19657,7 @@
         <v>142.53176</v>
       </c>
       <c r="H484">
-        <v>373.12822</v>
+        <v>332.0423524</v>
       </c>
     </row>
     <row r="485" spans="1:8">
@@ -19683,7 +19683,7 @@
         <v>138.72896</v>
       </c>
       <c r="H485">
-        <v>373.16968</v>
+        <v>330.4775373</v>
       </c>
     </row>
     <row r="486" spans="1:8">
@@ -19709,7 +19709,7 @@
         <v>275.34</v>
       </c>
       <c r="H486">
-        <v>670.42018</v>
+        <v>613.6927598</v>
       </c>
     </row>
     <row r="487" spans="1:8">
@@ -19735,7 +19735,7 @@
         <v>179.40739</v>
       </c>
       <c r="H487">
-        <v>382.27736</v>
+        <v>360.2608248</v>
       </c>
     </row>
     <row r="488" spans="1:8">
@@ -19761,7 +19761,7 @@
         <v>169.63353</v>
       </c>
       <c r="H488">
-        <v>355.27244</v>
+        <v>355.2724355</v>
       </c>
     </row>
     <row r="489" spans="1:8">
@@ -19787,7 +19787,7 @@
         <v>195.83672</v>
       </c>
       <c r="H489">
-        <v>530.21817</v>
+        <v>577.3101684</v>
       </c>
     </row>
     <row r="490" spans="1:8">
@@ -19839,7 +19839,7 @@
         <v>50.97674</v>
       </c>
       <c r="H491">
-        <v>220.2094</v>
+        <v>220.2094037</v>
       </c>
     </row>
     <row r="492" spans="1:8">
@@ -19865,7 +19865,7 @@
         <v>145.1405</v>
       </c>
       <c r="H492">
-        <v>389.08491</v>
+        <v>389.0849088</v>
       </c>
     </row>
     <row r="493" spans="1:8">
@@ -19891,7 +19891,7 @@
         <v>45.08832</v>
       </c>
       <c r="H493">
-        <v>181.9016</v>
+        <v>181.9016045</v>
       </c>
     </row>
     <row r="494" spans="1:8">
@@ -19917,7 +19917,7 @@
         <v>38.74313</v>
       </c>
       <c r="H494">
-        <v>197.50188</v>
+        <v>197.5018805</v>
       </c>
     </row>
     <row r="495" spans="1:8">
@@ -19943,7 +19943,7 @@
         <v>77.22638999999999</v>
       </c>
       <c r="H495">
-        <v>325.30892</v>
+        <v>325.3089152</v>
       </c>
     </row>
     <row r="496" spans="1:8">
@@ -19969,7 +19969,7 @@
         <v>7.89444</v>
       </c>
       <c r="H496">
-        <v>85.31084</v>
+        <v>85.31084185</v>
       </c>
     </row>
     <row r="497" spans="1:8">
@@ -19995,7 +19995,7 @@
         <v>117.40764</v>
       </c>
       <c r="H497">
-        <v>366.51359</v>
+        <v>366.5135938</v>
       </c>
     </row>
     <row r="498" spans="1:8">
@@ -20021,7 +20021,7 @@
         <v>141.01008</v>
       </c>
       <c r="H498">
-        <v>367.9052</v>
+        <v>367.9052005</v>
       </c>
     </row>
     <row r="499" spans="1:8">
@@ -20047,7 +20047,7 @@
         <v>63.89539</v>
       </c>
       <c r="H499">
-        <v>247.10868</v>
+        <v>247.1086784</v>
       </c>
     </row>
     <row r="500" spans="1:8">
@@ -20073,7 +20073,7 @@
         <v>97.22451</v>
       </c>
       <c r="H500">
-        <v>351.74754</v>
+        <v>312.2701596</v>
       </c>
     </row>
     <row r="501" spans="1:8">
@@ -20099,7 +20099,7 @@
         <v>93.09058</v>
       </c>
       <c r="H501">
-        <v>347.68191</v>
+        <v>309.0880642</v>
       </c>
     </row>
     <row r="502" spans="1:8">
@@ -20125,7 +20125,7 @@
         <v>143.6625</v>
       </c>
       <c r="H502">
-        <v>560.8184</v>
+        <v>560.8183963</v>
       </c>
     </row>
     <row r="503" spans="1:8">
@@ -20151,7 +20151,7 @@
         <v>72.97607000000001</v>
       </c>
       <c r="H503">
-        <v>260.64223</v>
+        <v>281.2082237</v>
       </c>
     </row>
     <row r="504" spans="1:8">
@@ -20177,7 +20177,7 @@
         <v>126.78191</v>
       </c>
       <c r="H504">
-        <v>373.1095</v>
+        <v>328.8653921</v>
       </c>
     </row>
     <row r="505" spans="1:8">
@@ -20203,7 +20203,7 @@
         <v>116.37112</v>
       </c>
       <c r="H505">
-        <v>441.21034</v>
+        <v>347.4855584</v>
       </c>
     </row>
     <row r="506" spans="1:8">
@@ -20229,7 +20229,7 @@
         <v>51.08862</v>
       </c>
       <c r="H506">
-        <v>229.80995</v>
+        <v>229.8099475</v>
       </c>
     </row>
     <row r="507" spans="1:8">
@@ -20255,7 +20255,7 @@
         <v>124.0069</v>
       </c>
       <c r="H507">
-        <v>371.32819</v>
+        <v>326.0465578</v>
       </c>
     </row>
     <row r="508" spans="1:8">
@@ -20281,7 +20281,7 @@
         <v>120.51865</v>
       </c>
       <c r="H508">
-        <v>368.24598</v>
+        <v>323.926706</v>
       </c>
     </row>
     <row r="509" spans="1:8">
@@ -20307,7 +20307,7 @@
         <v>112.07522</v>
       </c>
       <c r="H509">
-        <v>392.40069</v>
+        <v>321.4788019</v>
       </c>
     </row>
     <row r="510" spans="1:8">
@@ -20333,7 +20333,7 @@
         <v>236.8046</v>
       </c>
       <c r="H510">
-        <v>881.70791</v>
+        <v>852.3231223</v>
       </c>
     </row>
     <row r="511" spans="1:8">
@@ -20359,7 +20359,7 @@
         <v>116.54258</v>
       </c>
       <c r="H511">
-        <v>421.3979</v>
+        <v>467.3738402</v>
       </c>
     </row>
     <row r="512" spans="1:8">
@@ -20385,7 +20385,7 @@
         <v>89.05741999999999</v>
       </c>
       <c r="H512">
-        <v>265.12778</v>
+        <v>265.1277814</v>
       </c>
     </row>
     <row r="513" spans="1:8">
@@ -20411,7 +20411,7 @@
         <v>128.04583</v>
       </c>
       <c r="H513">
-        <v>429.84388</v>
+        <v>393.7025568</v>
       </c>
     </row>
     <row r="514" spans="1:8">
@@ -20437,7 +20437,7 @@
         <v>151.39135</v>
       </c>
       <c r="H514">
-        <v>472.85217</v>
+        <v>539.3821022</v>
       </c>
     </row>
     <row r="515" spans="1:8">
@@ -20463,7 +20463,7 @@
         <v>162.92531</v>
       </c>
       <c r="H515">
-        <v>630.31874</v>
+        <v>630.3187409</v>
       </c>
     </row>
     <row r="516" spans="1:8">
@@ -20489,7 +20489,7 @@
         <v>9.07471</v>
       </c>
       <c r="H516">
-        <v>111.65512</v>
+        <v>190.6601541</v>
       </c>
     </row>
     <row r="517" spans="1:8">
@@ -20515,7 +20515,7 @@
         <v>113.11611</v>
       </c>
       <c r="H517">
-        <v>331.49672</v>
+        <v>284.4255239</v>
       </c>
     </row>
     <row r="518" spans="1:8">
@@ -20541,7 +20541,7 @@
         <v>117.5328</v>
       </c>
       <c r="H518">
-        <v>333.62227</v>
+        <v>284.8868234</v>
       </c>
     </row>
     <row r="519" spans="1:8">
@@ -20567,7 +20567,7 @@
         <v>102.06295</v>
       </c>
       <c r="H519">
-        <v>318.21709</v>
+        <v>318.2170869</v>
       </c>
     </row>
     <row r="520" spans="1:8">
@@ -20593,7 +20593,7 @@
         <v>124.25002</v>
       </c>
       <c r="H520">
-        <v>336.94101</v>
+        <v>336.9410124</v>
       </c>
     </row>
     <row r="521" spans="1:8">
@@ -20619,7 +20619,7 @@
         <v>94.01105</v>
       </c>
       <c r="H521">
-        <v>316.40345</v>
+        <v>276.2553059</v>
       </c>
     </row>
     <row r="522" spans="1:8">
@@ -20645,7 +20645,7 @@
         <v>100.65004</v>
       </c>
       <c r="H522">
-        <v>322.03341</v>
+        <v>281.706354</v>
       </c>
     </row>
     <row r="523" spans="1:8">
@@ -20671,7 +20671,7 @@
         <v>62.1648</v>
       </c>
       <c r="H523">
-        <v>224.06415</v>
+        <v>253.640911</v>
       </c>
     </row>
     <row r="524" spans="1:8">
@@ -20697,7 +20697,7 @@
         <v>119.19205</v>
       </c>
       <c r="H524">
-        <v>334.30231</v>
+        <v>286.7832511</v>
       </c>
     </row>
     <row r="525" spans="1:8">
@@ -20723,7 +20723,7 @@
         <v>68.31807000000001</v>
       </c>
       <c r="H525">
-        <v>246.67873</v>
+        <v>246.6787305</v>
       </c>
     </row>
     <row r="526" spans="1:8">
@@ -20749,7 +20749,7 @@
         <v>138.49534</v>
       </c>
       <c r="H526">
-        <v>377.94512</v>
+        <v>377.9451169</v>
       </c>
     </row>
     <row r="527" spans="1:8">
@@ -20775,7 +20775,7 @@
         <v>122.81712</v>
       </c>
       <c r="H527">
-        <v>337.87256</v>
+        <v>337.8725599</v>
       </c>
     </row>
     <row r="528" spans="1:8">
@@ -20801,7 +20801,7 @@
         <v>149.14985</v>
       </c>
       <c r="H528">
-        <v>468.2883</v>
+        <v>468.2882984</v>
       </c>
     </row>
     <row r="529" spans="1:8">
@@ -20827,7 +20827,7 @@
         <v>121.63493</v>
       </c>
       <c r="H529">
-        <v>534.00271</v>
+        <v>534.0027135</v>
       </c>
     </row>
     <row r="530" spans="1:8">
@@ -20853,7 +20853,7 @@
         <v>262.08513</v>
       </c>
       <c r="H530">
-        <v>593.70455</v>
+        <v>563.0637655</v>
       </c>
     </row>
     <row r="531" spans="1:8">
@@ -20879,7 +20879,7 @@
         <v>201.13498</v>
       </c>
       <c r="H531">
-        <v>620.28342</v>
+        <v>620.2834214</v>
       </c>
     </row>
     <row r="532" spans="1:8">
@@ -20905,7 +20905,7 @@
         <v>63.98367</v>
       </c>
       <c r="H532">
-        <v>259.3388</v>
+        <v>259.3387954</v>
       </c>
     </row>
     <row r="533" spans="1:8">
@@ -20931,7 +20931,7 @@
         <v>138.0385</v>
       </c>
       <c r="H533">
-        <v>356.23084</v>
+        <v>356.230844</v>
       </c>
     </row>
     <row r="534" spans="1:8">
@@ -20957,7 +20957,7 @@
         <v>325.26439</v>
       </c>
       <c r="H534">
-        <v>926.03674</v>
+        <v>833.4294781</v>
       </c>
     </row>
     <row r="535" spans="1:8">
@@ -20983,7 +20983,7 @@
         <v>106.27547</v>
       </c>
       <c r="H535">
-        <v>431.9272</v>
+        <v>431.9272009</v>
       </c>
     </row>
     <row r="536" spans="1:8">
@@ -21009,7 +21009,7 @@
         <v>117.01756</v>
       </c>
       <c r="H536">
-        <v>545.81359</v>
+        <v>599.6352949</v>
       </c>
     </row>
     <row r="537" spans="1:8">
@@ -21035,7 +21035,7 @@
         <v>30.0119</v>
       </c>
       <c r="H537">
-        <v>168.63425</v>
+        <v>168.6342543</v>
       </c>
     </row>
     <row r="538" spans="1:8">
@@ -21061,7 +21061,7 @@
         <v>90.31896999999999</v>
       </c>
       <c r="H538">
-        <v>391.26903</v>
+        <v>391.269032</v>
       </c>
     </row>
     <row r="539" spans="1:8">
@@ -21087,7 +21087,7 @@
         <v>95.83256</v>
       </c>
       <c r="H539">
-        <v>414.01063</v>
+        <v>414.0106259</v>
       </c>
     </row>
     <row r="540" spans="1:8">
@@ -21113,7 +21113,7 @@
         <v>102.66236</v>
       </c>
       <c r="H540">
-        <v>430.01166</v>
+        <v>430.0116594</v>
       </c>
     </row>
     <row r="541" spans="1:8">
@@ -21139,7 +21139,7 @@
         <v>136.33065</v>
       </c>
       <c r="H541">
-        <v>803.77964</v>
+        <v>803.7796381000001</v>
       </c>
     </row>
     <row r="542" spans="1:8">
@@ -21165,7 +21165,7 @@
         <v>48.93321</v>
       </c>
       <c r="H542">
-        <v>309.30173</v>
+        <v>309.301732</v>
       </c>
     </row>
     <row r="543" spans="1:8">
@@ -21191,7 +21191,7 @@
         <v>375.80737</v>
       </c>
       <c r="H543">
-        <v>1248.48966</v>
+        <v>1248.489663</v>
       </c>
     </row>
     <row r="544" spans="1:8">
@@ -21217,7 +21217,7 @@
         <v>115.80086</v>
       </c>
       <c r="H544">
-        <v>405.83068</v>
+        <v>346.7950989</v>
       </c>
     </row>
     <row r="545" spans="1:8">
@@ -21243,7 +21243,7 @@
         <v>146.91825</v>
       </c>
       <c r="H545">
-        <v>556.69487</v>
+        <v>556.6948685999999</v>
       </c>
     </row>
     <row r="546" spans="1:8">
@@ -21269,7 +21269,7 @@
         <v>74.93001</v>
       </c>
       <c r="H546">
-        <v>486.59341</v>
+        <v>454.0372532</v>
       </c>
     </row>
     <row r="547" spans="1:8">
@@ -21295,7 +21295,7 @@
         <v>158.73584</v>
       </c>
       <c r="H547">
-        <v>465.23589</v>
+        <v>465.2358919</v>
       </c>
     </row>
     <row r="548" spans="1:8">
@@ -21321,7 +21321,7 @@
         <v>209.37024</v>
       </c>
       <c r="H548">
-        <v>615.91239</v>
+        <v>623.2375994</v>
       </c>
     </row>
     <row r="549" spans="1:8">
@@ -21347,7 +21347,7 @@
         <v>118.74247</v>
       </c>
       <c r="H549">
-        <v>347.59997</v>
+        <v>347.5999739</v>
       </c>
     </row>
     <row r="550" spans="1:8">
@@ -21373,7 +21373,7 @@
         <v>86.62442</v>
       </c>
       <c r="H550">
-        <v>281.69674</v>
+        <v>274.0150625</v>
       </c>
     </row>
     <row r="551" spans="1:8">
@@ -21399,7 +21399,7 @@
         <v>92.9055</v>
       </c>
       <c r="H551">
-        <v>287.31825</v>
+        <v>264.387078</v>
       </c>
     </row>
     <row r="552" spans="1:8">
@@ -21425,7 +21425,7 @@
         <v>3.12681</v>
       </c>
       <c r="H552">
-        <v>46.08064</v>
+        <v>46.08063945</v>
       </c>
     </row>
     <row r="553" spans="1:8">
@@ -21451,7 +21451,7 @@
         <v>104.59117</v>
       </c>
       <c r="H553">
-        <v>297.03301</v>
+        <v>283.0545884</v>
       </c>
     </row>
     <row r="554" spans="1:8">
@@ -21477,7 +21477,7 @@
         <v>95.83868</v>
       </c>
       <c r="H554">
-        <v>287.08771</v>
+        <v>287.087707</v>
       </c>
     </row>
     <row r="555" spans="1:8">
@@ -21503,7 +21503,7 @@
         <v>105.28675</v>
       </c>
       <c r="H555">
-        <v>296.15989</v>
+        <v>288.3722007</v>
       </c>
     </row>
     <row r="556" spans="1:8">
@@ -21529,7 +21529,7 @@
         <v>155.96045</v>
       </c>
       <c r="H556">
-        <v>463.43112</v>
+        <v>463.4311241</v>
       </c>
     </row>
     <row r="557" spans="1:8">
@@ -21555,7 +21555,7 @@
         <v>85.00942000000001</v>
       </c>
       <c r="H557">
-        <v>286.94558</v>
+        <v>286.9455798</v>
       </c>
     </row>
     <row r="558" spans="1:8">
@@ -21581,7 +21581,7 @@
         <v>248.59915</v>
       </c>
       <c r="H558">
-        <v>655.3744</v>
+        <v>695.1398398</v>
       </c>
     </row>
     <row r="559" spans="1:8">
@@ -21607,7 +21607,7 @@
         <v>181.06393</v>
       </c>
       <c r="H559">
-        <v>708.90611</v>
+        <v>708.9061113</v>
       </c>
     </row>
     <row r="560" spans="1:8">
@@ -21633,7 +21633,7 @@
         <v>242.76571</v>
       </c>
       <c r="H560">
-        <v>627.64598</v>
+        <v>610.9191632</v>
       </c>
     </row>
     <row r="561" spans="1:8">
@@ -21659,7 +21659,7 @@
         <v>140.04121</v>
       </c>
       <c r="H561">
-        <v>473.04473</v>
+        <v>378.8882445</v>
       </c>
     </row>
     <row r="562" spans="1:8">
@@ -21685,7 +21685,7 @@
         <v>175.04669</v>
       </c>
       <c r="H562">
-        <v>592.01336</v>
+        <v>532.6748319</v>
       </c>
     </row>
     <row r="563" spans="1:8">
@@ -21711,7 +21711,7 @@
         <v>106.22362</v>
       </c>
       <c r="H563">
-        <v>372.57732</v>
+        <v>372.5773223</v>
       </c>
     </row>
     <row r="564" spans="1:8">
@@ -21737,7 +21737,7 @@
         <v>125.57968</v>
       </c>
       <c r="H564">
-        <v>459.05053</v>
+        <v>505.6208201</v>
       </c>
     </row>
     <row r="565" spans="1:8">
@@ -21763,7 +21763,7 @@
         <v>53.45393</v>
       </c>
       <c r="H565">
-        <v>197.78819</v>
+        <v>197.7881944</v>
       </c>
     </row>
     <row r="566" spans="1:8">
@@ -21789,7 +21789,7 @@
         <v>123.24072</v>
       </c>
       <c r="H566">
-        <v>765.75909</v>
+        <v>765.7590874</v>
       </c>
     </row>
     <row r="567" spans="1:8">
@@ -21815,7 +21815,7 @@
         <v>40.5775</v>
       </c>
       <c r="H567">
-        <v>298.0063</v>
+        <v>298.0063037</v>
       </c>
     </row>
     <row r="568" spans="1:8">
@@ -21841,7 +21841,7 @@
         <v>134.05091</v>
       </c>
       <c r="H568">
-        <v>428.63658</v>
+        <v>428.6365816</v>
       </c>
     </row>
     <row r="569" spans="1:8">
@@ -21867,7 +21867,7 @@
         <v>38.94768</v>
       </c>
       <c r="H569">
-        <v>236.94144</v>
+        <v>236.9414429</v>
       </c>
     </row>
     <row r="570" spans="1:8">
@@ -21893,7 +21893,7 @@
         <v>9.5383</v>
       </c>
       <c r="H570">
-        <v>203.55227</v>
+        <v>203.5522669</v>
       </c>
     </row>
     <row r="571" spans="1:8">
@@ -21919,7 +21919,7 @@
         <v>6.31153</v>
       </c>
       <c r="H571">
-        <v>168.95738</v>
+        <v>168.9573781</v>
       </c>
     </row>
     <row r="572" spans="1:8">
@@ -21945,7 +21945,7 @@
         <v>136.26963</v>
       </c>
       <c r="H572">
-        <v>569.70987</v>
+        <v>569.7098703</v>
       </c>
     </row>
     <row r="573" spans="1:8">
@@ -21971,7 +21971,7 @@
         <v>170.76186</v>
       </c>
       <c r="H573">
-        <v>373.59996</v>
+        <v>394.8994184</v>
       </c>
     </row>
     <row r="574" spans="1:8">
@@ -21997,7 +21997,7 @@
         <v>166.11077</v>
       </c>
       <c r="H574">
-        <v>375.05349</v>
+        <v>375.0534903</v>
       </c>
     </row>
     <row r="575" spans="1:8">
@@ -22023,7 +22023,7 @@
         <v>146.37791</v>
       </c>
       <c r="H575">
-        <v>359.68017</v>
+        <v>359.6801678</v>
       </c>
     </row>
     <row r="576" spans="1:8">
@@ -22049,7 +22049,7 @@
         <v>152.0941</v>
       </c>
       <c r="H576">
-        <v>406.88024</v>
+        <v>400.2449365</v>
       </c>
     </row>
     <row r="577" spans="1:8">
@@ -22075,7 +22075,7 @@
         <v>189.73904</v>
       </c>
       <c r="H577">
-        <v>383.38516</v>
+        <v>406.6378174</v>
       </c>
     </row>
     <row r="578" spans="1:8">
@@ -22101,7 +22101,7 @@
         <v>133.69224</v>
       </c>
       <c r="H578">
-        <v>361.49447</v>
+        <v>372.4740969</v>
       </c>
     </row>
     <row r="579" spans="1:8">
@@ -22127,7 +22127,7 @@
         <v>145.08925</v>
       </c>
       <c r="H579">
-        <v>367.45088</v>
+        <v>367.4508811</v>
       </c>
     </row>
     <row r="580" spans="1:8">
@@ -22153,7 +22153,7 @@
         <v>162.02017</v>
       </c>
       <c r="H580">
-        <v>375.14082</v>
+        <v>375.1408229</v>
       </c>
     </row>
     <row r="581" spans="1:8">
@@ -22179,7 +22179,7 @@
         <v>181.75894</v>
       </c>
       <c r="H581">
-        <v>383.09723</v>
+        <v>399.6379333</v>
       </c>
     </row>
     <row r="582" spans="1:8">
@@ -22205,7 +22205,7 @@
         <v>206.27913</v>
       </c>
       <c r="H582">
-        <v>664.85001</v>
+        <v>664.8500084</v>
       </c>
     </row>
     <row r="583" spans="1:8">
@@ -22231,7 +22231,7 @@
         <v>162.33939</v>
       </c>
       <c r="H583">
-        <v>477.51124</v>
+        <v>477.5112385</v>
       </c>
     </row>
     <row r="584" spans="1:8">
@@ -22257,7 +22257,7 @@
         <v>299.90058</v>
       </c>
       <c r="H584">
-        <v>925.71988</v>
+        <v>925.7198752</v>
       </c>
     </row>
     <row r="585" spans="1:8">
@@ -22283,7 +22283,7 @@
         <v>122.30249</v>
       </c>
       <c r="H585">
-        <v>305.23631</v>
+        <v>305.2363071</v>
       </c>
     </row>
     <row r="586" spans="1:8">
@@ -22309,7 +22309,7 @@
         <v>279.96718</v>
       </c>
       <c r="H586">
-        <v>823.09837</v>
+        <v>789.3813388</v>
       </c>
     </row>
     <row r="587" spans="1:8">
@@ -22335,7 +22335,7 @@
         <v>14.75924</v>
       </c>
       <c r="H587">
-        <v>141.53713</v>
+        <v>141.5371253</v>
       </c>
     </row>
     <row r="588" spans="1:8">
@@ -22361,7 +22361,7 @@
         <v>78.60468</v>
       </c>
       <c r="H588">
-        <v>493.12599</v>
+        <v>493.1259893</v>
       </c>
     </row>
     <row r="589" spans="1:8">
@@ -22387,7 +22387,7 @@
         <v>96.96245999999999</v>
       </c>
       <c r="H589">
-        <v>319.47185</v>
+        <v>319.4718534</v>
       </c>
     </row>
     <row r="590" spans="1:8">
@@ -22413,7 +22413,7 @@
         <v>210.19156</v>
       </c>
       <c r="H590">
-        <v>429.86593</v>
+        <v>393.2967641</v>
       </c>
     </row>
     <row r="591" spans="1:8">
@@ -22439,7 +22439,7 @@
         <v>202.10048</v>
       </c>
       <c r="H591">
-        <v>432.48968</v>
+        <v>432.4896804</v>
       </c>
     </row>
     <row r="592" spans="1:8">
@@ -22465,7 +22465,7 @@
         <v>107.23786</v>
       </c>
       <c r="H592">
-        <v>405.44737</v>
+        <v>405.4473742</v>
       </c>
     </row>
     <row r="593" spans="1:8">
@@ -22491,7 +22491,7 @@
         <v>252.75263</v>
       </c>
       <c r="H593">
-        <v>476.02173</v>
+        <v>476.0217271</v>
       </c>
     </row>
     <row r="594" spans="1:8">
@@ -22517,7 +22517,7 @@
         <v>227.68164</v>
       </c>
       <c r="H594">
-        <v>508.01374</v>
+        <v>452.5431795</v>
       </c>
     </row>
     <row r="595" spans="1:8">
@@ -22543,7 +22543,7 @@
         <v>110.67797</v>
       </c>
       <c r="H595">
-        <v>297.25634</v>
+        <v>297.2563438</v>
       </c>
     </row>
     <row r="596" spans="1:8">
@@ -22569,7 +22569,7 @@
         <v>218.8075</v>
       </c>
       <c r="H596">
-        <v>484.60298</v>
+        <v>435.241269</v>
       </c>
     </row>
     <row r="597" spans="1:8">
@@ -22595,7 +22595,7 @@
         <v>62.94186</v>
       </c>
       <c r="H597">
-        <v>223.51773</v>
+        <v>151.2062251</v>
       </c>
     </row>
     <row r="598" spans="1:8">
@@ -22621,7 +22621,7 @@
         <v>239.29058</v>
       </c>
       <c r="H598">
-        <v>447.30355</v>
+        <v>447.3035463</v>
       </c>
     </row>
     <row r="599" spans="1:8">
@@ -22647,7 +22647,7 @@
         <v>28.94854</v>
       </c>
       <c r="H599">
-        <v>189.89065</v>
+        <v>189.564047</v>
       </c>
     </row>
     <row r="600" spans="1:8">
@@ -22673,7 +22673,7 @@
         <v>302.07267</v>
       </c>
       <c r="H600">
-        <v>594.02034</v>
+        <v>594.0203353000001</v>
       </c>
     </row>
     <row r="601" spans="1:8">
@@ -22699,7 +22699,7 @@
         <v>277.47066</v>
       </c>
       <c r="H601">
-        <v>674.3330099999999</v>
+        <v>674.3330099</v>
       </c>
     </row>
     <row r="602" spans="1:8">
@@ -22725,7 +22725,7 @@
         <v>173.82278</v>
       </c>
       <c r="H602">
-        <v>418.14832</v>
+        <v>418.1483176</v>
       </c>
     </row>
     <row r="603" spans="1:8">
@@ -22751,7 +22751,7 @@
         <v>31.46832</v>
       </c>
       <c r="H603">
-        <v>246.29278</v>
+        <v>246.2927825</v>
       </c>
     </row>
     <row r="604" spans="1:8">
@@ -22777,7 +22777,7 @@
         <v>31.1648</v>
       </c>
       <c r="H604">
-        <v>224.57572</v>
+        <v>166.3697649</v>
       </c>
     </row>
     <row r="605" spans="1:8">
@@ -22803,7 +22803,7 @@
         <v>53.36051</v>
       </c>
       <c r="H605">
-        <v>341.86952</v>
+        <v>341.8695246</v>
       </c>
     </row>
     <row r="606" spans="1:8">
@@ -22855,7 +22855,7 @@
         <v>151.68168</v>
       </c>
       <c r="H607">
-        <v>403.603</v>
+        <v>403.6029986</v>
       </c>
     </row>
     <row r="608" spans="1:8">
@@ -22881,7 +22881,7 @@
         <v>238.92537</v>
       </c>
       <c r="H608">
-        <v>642.0313599999999</v>
+        <v>642.0313626</v>
       </c>
     </row>
     <row r="609" spans="1:8">
@@ -22907,7 +22907,7 @@
         <v>368.71296</v>
       </c>
       <c r="H609">
-        <v>646.89103</v>
+        <v>646.8910268</v>
       </c>
     </row>
     <row r="610" spans="1:8">
@@ -22933,7 +22933,7 @@
         <v>120.01189</v>
       </c>
       <c r="H610">
-        <v>313.21068</v>
+        <v>313.2106826</v>
       </c>
     </row>
     <row r="611" spans="1:8">
@@ -22959,7 +22959,7 @@
         <v>150.48902</v>
       </c>
       <c r="H611">
-        <v>319.48581</v>
+        <v>319.4858119</v>
       </c>
     </row>
     <row r="612" spans="1:8">
@@ -22985,7 +22985,7 @@
         <v>104.66499</v>
       </c>
       <c r="H612">
-        <v>270.10933</v>
+        <v>270.109327</v>
       </c>
     </row>
     <row r="613" spans="1:8">
@@ -23011,7 +23011,7 @@
         <v>23.4787</v>
       </c>
       <c r="H613">
-        <v>147.09052</v>
+        <v>147.0905185</v>
       </c>
     </row>
     <row r="614" spans="1:8">
@@ -23037,7 +23037,7 @@
         <v>177.55285</v>
       </c>
       <c r="H614">
-        <v>397.53063</v>
+        <v>397.5306287</v>
       </c>
     </row>
     <row r="615" spans="1:8">
@@ -23063,7 +23063,7 @@
         <v>84.49818999999999</v>
       </c>
       <c r="H615">
-        <v>297.19948</v>
+        <v>297.1994789</v>
       </c>
     </row>
     <row r="616" spans="1:8">
@@ -23089,7 +23089,7 @@
         <v>167.7937</v>
       </c>
       <c r="H616">
-        <v>395.32096</v>
+        <v>395.3209573</v>
       </c>
     </row>
     <row r="617" spans="1:8">
@@ -23115,7 +23115,7 @@
         <v>154.98824</v>
       </c>
       <c r="H617">
-        <v>320.57557</v>
+        <v>320.575574</v>
       </c>
     </row>
     <row r="618" spans="1:8">
@@ -23141,7 +23141,7 @@
         <v>147.57634</v>
       </c>
       <c r="H618">
-        <v>402.02907</v>
+        <v>379.5644918</v>
       </c>
     </row>
     <row r="619" spans="1:8">
@@ -23167,7 +23167,7 @@
         <v>131.27554</v>
       </c>
       <c r="H619">
-        <v>386.14003</v>
+        <v>413.7166843</v>
       </c>
     </row>
     <row r="620" spans="1:8">
@@ -23193,7 +23193,7 @@
         <v>161.84071</v>
       </c>
       <c r="H620">
-        <v>318.29325</v>
+        <v>318.293246</v>
       </c>
     </row>
     <row r="621" spans="1:8">
@@ -23219,7 +23219,7 @@
         <v>23.12762</v>
       </c>
       <c r="H621">
-        <v>165.05517</v>
+        <v>165.0551725</v>
       </c>
     </row>
     <row r="622" spans="1:8">
@@ -23245,7 +23245,7 @@
         <v>119.47354</v>
       </c>
       <c r="H622">
-        <v>333.90129</v>
+        <v>252.6562765</v>
       </c>
     </row>
     <row r="623" spans="1:8">
@@ -23271,7 +23271,7 @@
         <v>146.574</v>
       </c>
       <c r="H623">
-        <v>395.22265</v>
+        <v>395.2226483</v>
       </c>
     </row>
     <row r="624" spans="1:8">
@@ -23297,7 +23297,7 @@
         <v>162.37204</v>
       </c>
       <c r="H624">
-        <v>382.77223</v>
+        <v>457.075154</v>
       </c>
     </row>
     <row r="625" spans="1:8">
@@ -23323,7 +23323,7 @@
         <v>111.51322</v>
       </c>
       <c r="H625">
-        <v>349.74313</v>
+        <v>349.7431286</v>
       </c>
     </row>
     <row r="626" spans="1:8">
@@ -23349,7 +23349,7 @@
         <v>111.44956</v>
       </c>
       <c r="H626">
-        <v>350.81389</v>
+        <v>350.8138921</v>
       </c>
     </row>
     <row r="627" spans="1:8">
@@ -23375,7 +23375,7 @@
         <v>174.08028</v>
       </c>
       <c r="H627">
-        <v>432.77543</v>
+        <v>432.7754298</v>
       </c>
     </row>
     <row r="628" spans="1:8">
@@ -23401,7 +23401,7 @@
         <v>145.13528</v>
       </c>
       <c r="H628">
-        <v>384.71736</v>
+        <v>384.7173586</v>
       </c>
     </row>
     <row r="629" spans="1:8">
@@ -23427,7 +23427,7 @@
         <v>198.55165</v>
       </c>
       <c r="H629">
-        <v>437.04177</v>
+        <v>452.0670997</v>
       </c>
     </row>
     <row r="630" spans="1:8">
@@ -23453,7 +23453,7 @@
         <v>191.0415</v>
       </c>
       <c r="H630">
-        <v>475.83001</v>
+        <v>475.8300082</v>
       </c>
     </row>
     <row r="631" spans="1:8">
@@ -23479,7 +23479,7 @@
         <v>195.26117</v>
       </c>
       <c r="H631">
-        <v>469.58404</v>
+        <v>480.0954308</v>
       </c>
     </row>
     <row r="632" spans="1:8">
@@ -23505,7 +23505,7 @@
         <v>204.93589</v>
       </c>
       <c r="H632">
-        <v>412.75583</v>
+        <v>412.7558325</v>
       </c>
     </row>
     <row r="633" spans="1:8">
@@ -23531,7 +23531,7 @@
         <v>193.86806</v>
       </c>
       <c r="H633">
-        <v>453.1827</v>
+        <v>392.6746987</v>
       </c>
     </row>
     <row r="634" spans="1:8">
@@ -23557,7 +23557,7 @@
         <v>215.22006</v>
       </c>
       <c r="H634">
-        <v>379.30721</v>
+        <v>379.3072128</v>
       </c>
     </row>
     <row r="635" spans="1:8">
@@ -23583,7 +23583,7 @@
         <v>267.54708</v>
       </c>
       <c r="H635">
-        <v>433.42757</v>
+        <v>433.4275696</v>
       </c>
     </row>
     <row r="636" spans="1:8">
@@ -23609,7 +23609,7 @@
         <v>208.31693</v>
       </c>
       <c r="H636">
-        <v>367.21267</v>
+        <v>367.2126714</v>
       </c>
     </row>
     <row r="637" spans="1:8">
@@ -23635,7 +23635,7 @@
         <v>235.47065</v>
       </c>
       <c r="H637">
-        <v>411.05481</v>
+        <v>398.330129</v>
       </c>
     </row>
     <row r="638" spans="1:8">
@@ -23661,7 +23661,7 @@
         <v>105.3226</v>
       </c>
       <c r="H638">
-        <v>294.00294</v>
+        <v>294.0029436</v>
       </c>
     </row>
     <row r="639" spans="1:8">
@@ -23687,7 +23687,7 @@
         <v>240.50774</v>
       </c>
       <c r="H639">
-        <v>401.86998</v>
+        <v>401.869983</v>
       </c>
     </row>
     <row r="640" spans="1:8">
@@ -23713,7 +23713,7 @@
         <v>94.12732</v>
       </c>
       <c r="H640">
-        <v>299.47795</v>
+        <v>299.4779536</v>
       </c>
     </row>
     <row r="641" spans="1:8">
@@ -23739,7 +23739,7 @@
         <v>180.47629</v>
       </c>
       <c r="H641">
-        <v>646.46491</v>
+        <v>557.4656279</v>
       </c>
     </row>
     <row r="642" spans="1:8">
@@ -23765,7 +23765,7 @@
         <v>32.49898</v>
       </c>
       <c r="H642">
-        <v>273.9857</v>
+        <v>287.4421541</v>
       </c>
     </row>
     <row r="643" spans="1:8">
@@ -23791,7 +23791,7 @@
         <v>159.21935</v>
       </c>
       <c r="H643">
-        <v>949.4759299999999</v>
+        <v>890.8108342</v>
       </c>
     </row>
     <row r="644" spans="1:8">
@@ -23817,7 +23817,7 @@
         <v>282.55396</v>
       </c>
       <c r="H644">
-        <v>902.1678000000001</v>
+        <v>861.7396261</v>
       </c>
     </row>
     <row r="645" spans="1:8">
@@ -23843,7 +23843,7 @@
         <v>75.04331999999999</v>
       </c>
       <c r="H645">
-        <v>486.43774</v>
+        <v>486.4377386</v>
       </c>
     </row>
     <row r="646" spans="1:8">
@@ -23869,7 +23869,7 @@
         <v>137.31066</v>
       </c>
       <c r="H646">
-        <v>428.32636</v>
+        <v>428.326364</v>
       </c>
     </row>
     <row r="647" spans="1:8">
@@ -23895,7 +23895,7 @@
         <v>199.92773</v>
       </c>
       <c r="H647">
-        <v>379.37481</v>
+        <v>441.8098007</v>
       </c>
     </row>
     <row r="648" spans="1:8">
@@ -23921,7 +23921,7 @@
         <v>241.16565</v>
       </c>
       <c r="H648">
-        <v>468.85112</v>
+        <v>474.2905771</v>
       </c>
     </row>
     <row r="649" spans="1:8">
@@ -23947,7 +23947,7 @@
         <v>207.99774</v>
       </c>
       <c r="H649">
-        <v>447.89258</v>
+        <v>510.3771246</v>
       </c>
     </row>
     <row r="650" spans="1:8">
@@ -23973,7 +23973,7 @@
         <v>41.24408</v>
       </c>
       <c r="H650">
-        <v>235.1113</v>
+        <v>235.1112993</v>
       </c>
     </row>
     <row r="651" spans="1:8">
@@ -23999,7 +23999,7 @@
         <v>121.82016</v>
       </c>
       <c r="H651">
-        <v>412.12363</v>
+        <v>412.1236304</v>
       </c>
     </row>
     <row r="652" spans="1:8">
@@ -24025,7 +24025,7 @@
         <v>227.47702</v>
       </c>
       <c r="H652">
-        <v>460.99487</v>
+        <v>475.5379368</v>
       </c>
     </row>
     <row r="653" spans="1:8">
@@ -24051,7 +24051,7 @@
         <v>218.82807</v>
       </c>
       <c r="H653">
-        <v>510.50085</v>
+        <v>477.7939489</v>
       </c>
     </row>
     <row r="654" spans="1:8">
@@ -24077,7 +24077,7 @@
         <v>112.01069</v>
       </c>
       <c r="H654">
-        <v>450.99024</v>
+        <v>450.9902356</v>
       </c>
     </row>
     <row r="655" spans="1:8">
@@ -24103,7 +24103,7 @@
         <v>67.52066000000001</v>
       </c>
       <c r="H655">
-        <v>309.24894</v>
+        <v>309.2489436</v>
       </c>
     </row>
     <row r="656" spans="1:8">
@@ -24129,7 +24129,7 @@
         <v>222.35891</v>
       </c>
       <c r="H656">
-        <v>507.48916</v>
+        <v>483.9350858</v>
       </c>
     </row>
     <row r="657" spans="1:8">
@@ -24155,7 +24155,7 @@
         <v>213.68815</v>
       </c>
       <c r="H657">
-        <v>454.83382</v>
+        <v>454.8338225</v>
       </c>
     </row>
     <row r="658" spans="1:8">
@@ -24181,7 +24181,7 @@
         <v>232.7631</v>
       </c>
       <c r="H658">
-        <v>486.46419</v>
+        <v>448.7084989</v>
       </c>
     </row>
     <row r="659" spans="1:8">
@@ -24207,7 +24207,7 @@
         <v>216.271</v>
       </c>
       <c r="H659">
-        <v>395.3165</v>
+        <v>461.7699763</v>
       </c>
     </row>
     <row r="660" spans="1:8">
@@ -24233,7 +24233,7 @@
         <v>181.35205</v>
       </c>
       <c r="H660">
-        <v>421.31404</v>
+        <v>384.4903494</v>
       </c>
     </row>
     <row r="661" spans="1:8">
@@ -24259,7 +24259,7 @@
         <v>231.36344</v>
       </c>
       <c r="H661">
-        <v>545.63522</v>
+        <v>452.6657547</v>
       </c>
     </row>
     <row r="662" spans="1:8">
@@ -24285,7 +24285,7 @@
         <v>200.22937</v>
       </c>
       <c r="H662">
-        <v>542.91297</v>
+        <v>542.9129692</v>
       </c>
     </row>
     <row r="663" spans="1:8">
@@ -24311,7 +24311,7 @@
         <v>152.12673</v>
       </c>
       <c r="H663">
-        <v>423.73627</v>
+        <v>406.5363224</v>
       </c>
     </row>
     <row r="664" spans="1:8">
@@ -24337,7 +24337,7 @@
         <v>249.90984</v>
       </c>
       <c r="H664">
-        <v>826.09083</v>
+        <v>742.794402</v>
       </c>
     </row>
     <row r="665" spans="1:8">
@@ -24363,7 +24363,7 @@
         <v>263.75297</v>
       </c>
       <c r="H665">
-        <v>610.15625</v>
+        <v>610.1562544</v>
       </c>
     </row>
     <row r="666" spans="1:8">
@@ -24389,7 +24389,7 @@
         <v>257.12544</v>
       </c>
       <c r="H666">
-        <v>713.9062</v>
+        <v>713.9062016</v>
       </c>
     </row>
     <row r="667" spans="1:8">
